--- a/research/traditional_assets/database/data/mauritius/mauritius_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_construction_supplies.xlsx
@@ -1132,7 +1132,7 @@
         <v>48</v>
       </c>
       <c r="L2">
-        <v>9.33059858484345</v>
+        <v>9.33059858484344</v>
       </c>
       <c r="M2">
         <v>48</v>
@@ -1150,7 +1150,7 @@
         <v>0.09777734252425239</v>
       </c>
       <c r="R2">
-        <v>0.09224039736619651</v>
+        <v>0.0922403973661966</v>
       </c>
       <c r="S2">
         <v>0.0676324552648979</v>
@@ -1172,7 +1172,7 @@
         <v>0.09777734252425239</v>
       </c>
       <c r="X2">
-        <v>0.329726233538728</v>
+        <v>0.329726233538729</v>
       </c>
       <c r="Y2">
         <v>0.715487684377053</v>
@@ -1259,7 +1259,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1396,22 +1396,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09777734252425235</v>
+        <v>0.09766892651046596</v>
       </c>
       <c r="C2">
-        <v>48</v>
+        <v>47.55126541672123</v>
       </c>
       <c r="D2">
-        <v>48</v>
+        <v>48.03126541672123</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1432,28 +1432,28 @@
         <v>10.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.024144</v>
       </c>
       <c r="N2">
-        <v>10.1</v>
+        <v>10.075856</v>
       </c>
       <c r="O2">
-        <v>1.515</v>
+        <v>1.5113784</v>
       </c>
       <c r="P2">
-        <v>8.584999999999999</v>
+        <v>8.5644776</v>
       </c>
       <c r="Q2">
-        <v>-1.515000000000001</v>
+        <v>-1.5355224</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09777734252425235</v>
+        <v>0.09822361263683431</v>
       </c>
       <c r="T2">
-        <v>0.7154876843770529</v>
+        <v>0.7216307604550376</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>418.3233929754805</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1478,22 +1478,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09766892651046596</v>
+        <v>0.09756051049667959</v>
       </c>
       <c r="C3">
-        <v>47.55126541672123</v>
+        <v>47.10257159025169</v>
       </c>
       <c r="D3">
-        <v>48.03126541672123</v>
+        <v>48.06257159025169</v>
       </c>
       <c r="E3">
-        <v>0.48</v>
+        <v>0.96</v>
       </c>
       <c r="F3">
-        <v>0.48</v>
+        <v>0.96</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1514,28 +1514,28 @@
         <v>10.1</v>
       </c>
       <c r="M3">
-        <v>0.024144</v>
+        <v>0.048288</v>
       </c>
       <c r="N3">
-        <v>10.075856</v>
+        <v>10.051712</v>
       </c>
       <c r="O3">
-        <v>1.5113784</v>
+        <v>1.5077568</v>
       </c>
       <c r="P3">
-        <v>8.5644776</v>
+        <v>8.543955200000001</v>
       </c>
       <c r="Q3">
-        <v>-1.5355224</v>
+        <v>-1.556044799999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09822361263683431</v>
+        <v>0.09867899030273428</v>
       </c>
       <c r="T3">
-        <v>0.7216307604550376</v>
+        <v>0.7278992054325732</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>418.3233929754805</v>
+        <v>209.1616964877402</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1560,22 +1560,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09756051049667959</v>
+        <v>0.09745209448289321</v>
       </c>
       <c r="C4">
-        <v>47.10257159025169</v>
+        <v>46.65391860033773</v>
       </c>
       <c r="D4">
-        <v>48.06257159025169</v>
+        <v>48.09391860033772</v>
       </c>
       <c r="E4">
-        <v>0.96</v>
+        <v>1.44</v>
       </c>
       <c r="F4">
-        <v>0.96</v>
+        <v>1.44</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1596,28 +1596,28 @@
         <v>10.1</v>
       </c>
       <c r="M4">
-        <v>0.048288</v>
+        <v>0.072432</v>
       </c>
       <c r="N4">
-        <v>10.051712</v>
+        <v>10.027568</v>
       </c>
       <c r="O4">
-        <v>1.5077568</v>
+        <v>1.5041352</v>
       </c>
       <c r="P4">
-        <v>8.543955200000001</v>
+        <v>8.5234328</v>
       </c>
       <c r="Q4">
-        <v>-1.556044799999999</v>
+        <v>-1.5765672</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09867899030273428</v>
+        <v>0.09914375719885898</v>
       </c>
       <c r="T4">
-        <v>0.7278992054325732</v>
+        <v>0.7342968966983052</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>209.1616964877402</v>
+        <v>139.4411309918268</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1642,22 +1642,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09745209448289321</v>
+        <v>0.09734367846910683</v>
       </c>
       <c r="C5">
-        <v>46.65391860033773</v>
+        <v>46.20530652693379</v>
       </c>
       <c r="D5">
-        <v>48.09391860033772</v>
+        <v>48.12530652693379</v>
       </c>
       <c r="E5">
-        <v>1.44</v>
+        <v>1.92</v>
       </c>
       <c r="F5">
-        <v>1.44</v>
+        <v>1.92</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1678,28 +1678,28 @@
         <v>10.1</v>
       </c>
       <c r="M5">
-        <v>0.072432</v>
+        <v>0.096576</v>
       </c>
       <c r="N5">
-        <v>10.027568</v>
+        <v>10.003424</v>
       </c>
       <c r="O5">
-        <v>1.5041352</v>
+        <v>1.5005136</v>
       </c>
       <c r="P5">
-        <v>8.5234328</v>
+        <v>8.502910399999999</v>
       </c>
       <c r="Q5">
-        <v>-1.5765672</v>
+        <v>-1.5970896</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09914375719885898</v>
+        <v>0.09961820673865296</v>
       </c>
       <c r="T5">
-        <v>0.7342968966983052</v>
+        <v>0.7408278731987402</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>139.4411309918268</v>
+        <v>104.5808482438701</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1724,22 +1724,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09734367846910683</v>
+        <v>0.09723526245532044</v>
       </c>
       <c r="C6">
-        <v>46.20530652693379</v>
+        <v>45.75673545020326</v>
       </c>
       <c r="D6">
-        <v>48.12530652693379</v>
+        <v>48.15673545020326</v>
       </c>
       <c r="E6">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="F6">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1760,28 +1760,28 @@
         <v>10.1</v>
       </c>
       <c r="M6">
-        <v>0.096576</v>
+        <v>0.12072</v>
       </c>
       <c r="N6">
-        <v>10.003424</v>
+        <v>9.979279999999999</v>
       </c>
       <c r="O6">
-        <v>1.5005136</v>
+        <v>1.496892</v>
       </c>
       <c r="P6">
-        <v>8.502910399999999</v>
+        <v>8.482388</v>
       </c>
       <c r="Q6">
-        <v>-1.5970896</v>
+        <v>-1.617611999999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09961820673865296</v>
+        <v>0.100102644689811</v>
       </c>
       <c r="T6">
-        <v>0.7408278731987402</v>
+        <v>0.7474963439412895</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>104.5808482438701</v>
+        <v>83.66467859509608</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1806,22 +1806,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09723526245532044</v>
+        <v>0.09712684644153406</v>
       </c>
       <c r="C7">
-        <v>45.75673545020326</v>
+        <v>45.30820545051897</v>
       </c>
       <c r="D7">
-        <v>48.15673545020326</v>
+        <v>48.18820545051897</v>
       </c>
       <c r="E7">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="F7">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1842,28 +1842,28 @@
         <v>10.1</v>
       </c>
       <c r="M7">
-        <v>0.12072</v>
+        <v>0.144864</v>
       </c>
       <c r="N7">
-        <v>9.979279999999999</v>
+        <v>9.955136</v>
       </c>
       <c r="O7">
-        <v>1.496892</v>
+        <v>1.4932704</v>
       </c>
       <c r="P7">
-        <v>8.482388</v>
+        <v>8.461865599999999</v>
       </c>
       <c r="Q7">
-        <v>-1.617611999999999</v>
+        <v>-1.6381344</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.100102644689811</v>
+        <v>0.1005973898314192</v>
       </c>
       <c r="T7">
-        <v>0.7474963439412895</v>
+        <v>0.7543066970400631</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1880,7 +1880,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>83.66467859509608</v>
+        <v>69.72056549591339</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1888,22 +1888,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09712684644153405</v>
+        <v>0.09701843042774771</v>
       </c>
       <c r="C8">
-        <v>45.30820545051897</v>
+        <v>44.85971660846408</v>
       </c>
       <c r="D8">
-        <v>48.18820545051897</v>
+        <v>48.21971660846408</v>
       </c>
       <c r="E8">
-        <v>2.88</v>
+        <v>3.359999999999999</v>
       </c>
       <c r="F8">
-        <v>2.88</v>
+        <v>3.359999999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1924,28 +1924,28 @@
         <v>10.1</v>
       </c>
       <c r="M8">
-        <v>0.144864</v>
+        <v>0.169008</v>
       </c>
       <c r="N8">
-        <v>9.955136</v>
+        <v>9.930992</v>
       </c>
       <c r="O8">
-        <v>1.4932704</v>
+        <v>1.4896488</v>
       </c>
       <c r="P8">
-        <v>8.461865599999999</v>
+        <v>8.4413432</v>
       </c>
       <c r="Q8">
-        <v>-1.6381344</v>
+        <v>-1.658656799999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1005973898314192</v>
+        <v>0.1011027746534922</v>
       </c>
       <c r="T8">
-        <v>0.7543066970400631</v>
+        <v>0.7612635093452622</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>69.72056549591341</v>
+        <v>59.76048471078293</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1970,22 +1970,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0970184304277477</v>
+        <v>0.09691001441396134</v>
       </c>
       <c r="C9">
-        <v>44.85971660846408</v>
+        <v>44.41126900483262</v>
       </c>
       <c r="D9">
-        <v>48.21971660846408</v>
+        <v>48.25126900483261</v>
       </c>
       <c r="E9">
-        <v>3.36</v>
+        <v>3.84</v>
       </c>
       <c r="F9">
-        <v>3.36</v>
+        <v>3.84</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2006,28 +2006,28 @@
         <v>10.1</v>
       </c>
       <c r="M9">
-        <v>0.169008</v>
+        <v>0.193152</v>
       </c>
       <c r="N9">
-        <v>9.930992</v>
+        <v>9.906848</v>
       </c>
       <c r="O9">
-        <v>1.4896488</v>
+        <v>1.4860272</v>
       </c>
       <c r="P9">
-        <v>8.4413432</v>
+        <v>8.4208208</v>
       </c>
       <c r="Q9">
-        <v>-1.658656799999999</v>
+        <v>-1.6791792</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1011027746534922</v>
+        <v>0.1016191461021319</v>
       </c>
       <c r="T9">
-        <v>0.7612635093452622</v>
+        <v>0.7683715567005742</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>59.76048471078291</v>
+        <v>52.29042412193506</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2052,22 +2052,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09691001441396134</v>
+        <v>0.09680159840017495</v>
       </c>
       <c r="C10">
-        <v>44.41126900483262</v>
+        <v>43.96286272063023</v>
       </c>
       <c r="D10">
-        <v>48.25126900483261</v>
+        <v>48.28286272063023</v>
       </c>
       <c r="E10">
-        <v>3.84</v>
+        <v>4.32</v>
       </c>
       <c r="F10">
-        <v>3.84</v>
+        <v>4.32</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2088,28 +2088,28 @@
         <v>10.1</v>
       </c>
       <c r="M10">
-        <v>0.193152</v>
+        <v>0.217296</v>
       </c>
       <c r="N10">
-        <v>9.906848</v>
+        <v>9.882704</v>
       </c>
       <c r="O10">
-        <v>1.4860272</v>
+        <v>1.4824056</v>
       </c>
       <c r="P10">
-        <v>8.4208208</v>
+        <v>8.4002984</v>
       </c>
       <c r="Q10">
-        <v>-1.6791792</v>
+        <v>-1.699701599999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1016191461021319</v>
+        <v>0.1021468663738186</v>
       </c>
       <c r="T10">
-        <v>0.7683715567005742</v>
+        <v>0.775635824876882</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>52.29042412193506</v>
+        <v>46.48037699727561</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2134,22 +2134,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09680159840017495</v>
+        <v>0.09669318238638858</v>
       </c>
       <c r="C11">
-        <v>43.96286272063023</v>
+        <v>43.51449783707486</v>
       </c>
       <c r="D11">
-        <v>48.28286272063023</v>
+        <v>48.31449783707485</v>
       </c>
       <c r="E11">
-        <v>4.32</v>
+        <v>4.8</v>
       </c>
       <c r="F11">
-        <v>4.32</v>
+        <v>4.8</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2170,28 +2170,28 @@
         <v>10.1</v>
       </c>
       <c r="M11">
-        <v>0.217296</v>
+        <v>0.24144</v>
       </c>
       <c r="N11">
-        <v>9.882704</v>
+        <v>9.858559999999999</v>
       </c>
       <c r="O11">
-        <v>1.4824056</v>
+        <v>1.478784</v>
       </c>
       <c r="P11">
-        <v>8.4002984</v>
+        <v>8.379776</v>
       </c>
       <c r="Q11">
-        <v>-1.699701599999999</v>
+        <v>-1.720224</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1021468663738186</v>
+        <v>0.102686313762654</v>
       </c>
       <c r="T11">
-        <v>0.775635824876882</v>
+        <v>0.7830615212348857</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>46.48037699727561</v>
+        <v>41.83233929754805</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2216,22 +2216,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09669318238638858</v>
+        <v>0.09658476637260219</v>
       </c>
       <c r="C12">
-        <v>43.51449783707486</v>
+        <v>43.06617443559744</v>
       </c>
       <c r="D12">
-        <v>48.31449783707485</v>
+        <v>48.34617443559744</v>
       </c>
       <c r="E12">
-        <v>4.800000000000001</v>
+        <v>5.28</v>
       </c>
       <c r="F12">
-        <v>4.800000000000001</v>
+        <v>5.28</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2252,28 +2252,28 @@
         <v>10.1</v>
       </c>
       <c r="M12">
-        <v>0.24144</v>
+        <v>0.265584</v>
       </c>
       <c r="N12">
-        <v>9.858559999999999</v>
+        <v>9.834415999999999</v>
       </c>
       <c r="O12">
-        <v>1.478784</v>
+        <v>1.4751624</v>
       </c>
       <c r="P12">
-        <v>8.379776</v>
+        <v>8.359253599999999</v>
       </c>
       <c r="Q12">
-        <v>-1.720224</v>
+        <v>-1.740746400000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.102686313762654</v>
+        <v>0.1032378835647215</v>
       </c>
       <c r="T12">
-        <v>0.7830615212348857</v>
+        <v>0.790654087173968</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>41.83233929754804</v>
+        <v>38.02939936140731</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2298,22 +2298,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09658476637260219</v>
+        <v>0.09647635035881581</v>
       </c>
       <c r="C13">
-        <v>43.06617443559744</v>
+        <v>42.61789259784261</v>
       </c>
       <c r="D13">
-        <v>48.34617443559744</v>
+        <v>48.3778925978426</v>
       </c>
       <c r="E13">
-        <v>5.28</v>
+        <v>5.76</v>
       </c>
       <c r="F13">
-        <v>5.28</v>
+        <v>5.76</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2334,28 +2334,28 @@
         <v>10.1</v>
       </c>
       <c r="M13">
-        <v>0.265584</v>
+        <v>0.289728</v>
       </c>
       <c r="N13">
-        <v>9.834415999999999</v>
+        <v>9.810271999999999</v>
       </c>
       <c r="O13">
-        <v>1.4751624</v>
+        <v>1.4715408</v>
       </c>
       <c r="P13">
-        <v>8.359253599999999</v>
+        <v>8.3387312</v>
       </c>
       <c r="Q13">
-        <v>-1.740746400000001</v>
+        <v>-1.7612688</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1032378835647215</v>
+        <v>0.1038019890441089</v>
       </c>
       <c r="T13">
-        <v>0.790654087173968</v>
+        <v>0.7984192114298477</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>38.02939936140731</v>
+        <v>34.8602827479567</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2380,22 +2380,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09647635035881581</v>
+        <v>0.09636793434502942</v>
       </c>
       <c r="C14">
-        <v>42.61789259784261</v>
+        <v>42.16965240566941</v>
       </c>
       <c r="D14">
-        <v>48.3778925978426</v>
+        <v>48.40965240566941</v>
       </c>
       <c r="E14">
-        <v>5.76</v>
+        <v>6.24</v>
       </c>
       <c r="F14">
-        <v>5.76</v>
+        <v>6.24</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2416,28 +2416,28 @@
         <v>10.1</v>
       </c>
       <c r="M14">
-        <v>0.289728</v>
+        <v>0.313872</v>
       </c>
       <c r="N14">
-        <v>9.810271999999999</v>
+        <v>9.786128</v>
       </c>
       <c r="O14">
-        <v>1.4715408</v>
+        <v>1.4679192</v>
       </c>
       <c r="P14">
-        <v>8.3387312</v>
+        <v>8.318208800000001</v>
       </c>
       <c r="Q14">
-        <v>-1.7612688</v>
+        <v>-1.781791199999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1038019890441089</v>
+        <v>0.1043790624655511</v>
       </c>
       <c r="T14">
-        <v>0.7984192114298477</v>
+        <v>0.8063628442893107</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>34.8602827479567</v>
+        <v>32.17872253657542</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2462,22 +2462,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09636793434502942</v>
+        <v>0.09625951833124305</v>
       </c>
       <c r="C15">
-        <v>42.16965240566941</v>
+        <v>41.72145394115197</v>
       </c>
       <c r="D15">
-        <v>48.40965240566941</v>
+        <v>48.44145394115197</v>
       </c>
       <c r="E15">
-        <v>6.24</v>
+        <v>6.720000000000001</v>
       </c>
       <c r="F15">
-        <v>6.24</v>
+        <v>6.720000000000001</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2498,28 +2498,28 @@
         <v>10.1</v>
       </c>
       <c r="M15">
-        <v>0.313872</v>
+        <v>0.338016</v>
       </c>
       <c r="N15">
-        <v>9.786128</v>
+        <v>9.761984</v>
       </c>
       <c r="O15">
-        <v>1.4679192</v>
+        <v>1.4642976</v>
       </c>
       <c r="P15">
-        <v>8.318208800000001</v>
+        <v>8.2976864</v>
       </c>
       <c r="Q15">
-        <v>-1.781791199999999</v>
+        <v>-1.8023136</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1043790624655511</v>
+        <v>0.1049695561991198</v>
       </c>
       <c r="T15">
-        <v>0.8063628442893107</v>
+        <v>0.8144912127966683</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>32.17872253657542</v>
+        <v>29.88024235539146</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2544,22 +2544,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09625951833124305</v>
+        <v>0.09615110231745667</v>
       </c>
       <c r="C16">
-        <v>41.72145394115197</v>
+        <v>41.27329728658023</v>
       </c>
       <c r="D16">
-        <v>48.44145394115197</v>
+        <v>48.47329728658023</v>
       </c>
       <c r="E16">
-        <v>6.720000000000001</v>
+        <v>7.200000000000001</v>
       </c>
       <c r="F16">
-        <v>6.720000000000001</v>
+        <v>7.200000000000001</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2580,28 +2580,28 @@
         <v>10.1</v>
       </c>
       <c r="M16">
-        <v>0.338016</v>
+        <v>0.36216</v>
       </c>
       <c r="N16">
-        <v>9.761984</v>
+        <v>9.73784</v>
       </c>
       <c r="O16">
-        <v>1.4642976</v>
+        <v>1.460676</v>
       </c>
       <c r="P16">
-        <v>8.2976864</v>
+        <v>8.277164000000001</v>
       </c>
       <c r="Q16">
-        <v>-1.8023136</v>
+        <v>-1.822835999999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1049695561991198</v>
+        <v>0.1055739439028902</v>
       </c>
       <c r="T16">
-        <v>0.8144912127966683</v>
+        <v>0.8228108370336108</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>29.88024235539146</v>
+        <v>27.88822619836536</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2626,22 +2626,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09615110231745667</v>
+        <v>0.09604268630367029</v>
       </c>
       <c r="C17">
-        <v>41.27329728658023</v>
+        <v>40.82518252446066</v>
       </c>
       <c r="D17">
-        <v>48.47329728658023</v>
+        <v>48.50518252446066</v>
       </c>
       <c r="E17">
-        <v>7.199999999999999</v>
+        <v>7.68</v>
       </c>
       <c r="F17">
-        <v>7.199999999999999</v>
+        <v>7.68</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2662,28 +2662,28 @@
         <v>10.1</v>
       </c>
       <c r="M17">
-        <v>0.3621599999999999</v>
+        <v>0.386304</v>
       </c>
       <c r="N17">
-        <v>9.73784</v>
+        <v>9.713695999999999</v>
       </c>
       <c r="O17">
-        <v>1.460676</v>
+        <v>1.4570544</v>
       </c>
       <c r="P17">
-        <v>8.277164000000001</v>
+        <v>8.256641599999998</v>
       </c>
       <c r="Q17">
-        <v>-1.822835999999999</v>
+        <v>-1.843358400000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1055739439028902</v>
+        <v>0.1061927217900837</v>
       </c>
       <c r="T17">
-        <v>0.8228108370336108</v>
+        <v>0.8313285475619091</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>27.88822619836537</v>
+        <v>26.14521206096753</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2708,22 +2708,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09604268630367029</v>
+        <v>0.09593427028988391</v>
       </c>
       <c r="C18">
-        <v>40.82518252446066</v>
+        <v>40.37710973751693</v>
       </c>
       <c r="D18">
-        <v>48.50518252446066</v>
+        <v>48.53710973751694</v>
       </c>
       <c r="E18">
-        <v>7.68</v>
+        <v>8.16</v>
       </c>
       <c r="F18">
-        <v>7.68</v>
+        <v>8.16</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2744,28 +2744,28 @@
         <v>10.1</v>
       </c>
       <c r="M18">
-        <v>0.386304</v>
+        <v>0.410448</v>
       </c>
       <c r="N18">
-        <v>9.713695999999999</v>
+        <v>9.689551999999999</v>
       </c>
       <c r="O18">
-        <v>1.4570544</v>
+        <v>1.4534328</v>
       </c>
       <c r="P18">
-        <v>8.256641599999998</v>
+        <v>8.236119199999999</v>
       </c>
       <c r="Q18">
-        <v>-1.843358400000001</v>
+        <v>-1.8638808</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1061927217900837</v>
+        <v>0.106826409987812</v>
       </c>
       <c r="T18">
-        <v>0.8313285475619091</v>
+        <v>0.8400515041270338</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>26.14521206096753</v>
+        <v>24.60725841032238</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2790,22 +2790,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09593427028988391</v>
+        <v>0.09582585427609754</v>
       </c>
       <c r="C19">
-        <v>40.37710973751693</v>
+        <v>39.92907900869071</v>
       </c>
       <c r="D19">
-        <v>48.53710973751694</v>
+        <v>48.56907900869071</v>
       </c>
       <c r="E19">
-        <v>8.16</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="F19">
-        <v>8.16</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2826,28 +2826,28 @@
         <v>10.1</v>
       </c>
       <c r="M19">
-        <v>0.410448</v>
+        <v>0.434592</v>
       </c>
       <c r="N19">
-        <v>9.689551999999999</v>
+        <v>9.665407999999999</v>
       </c>
       <c r="O19">
-        <v>1.4534328</v>
+        <v>1.4498112</v>
       </c>
       <c r="P19">
-        <v>8.236119199999999</v>
+        <v>8.2155968</v>
       </c>
       <c r="Q19">
-        <v>-1.8638808</v>
+        <v>-1.8844032</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.106826409987812</v>
+        <v>0.1074755539952409</v>
       </c>
       <c r="T19">
-        <v>0.8400515041270338</v>
+        <v>0.8489872157303322</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2864,7 +2864,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>24.60725841032238</v>
+        <v>23.2401884986378</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2872,22 +2872,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09582585427609755</v>
+        <v>0.09571743826231117</v>
       </c>
       <c r="C20">
-        <v>39.92907900869071</v>
+        <v>39.48109042114226</v>
       </c>
       <c r="D20">
-        <v>48.56907900869071</v>
+        <v>48.60109042114226</v>
       </c>
       <c r="E20">
-        <v>8.640000000000001</v>
+        <v>9.120000000000001</v>
       </c>
       <c r="F20">
-        <v>8.640000000000001</v>
+        <v>9.120000000000001</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2908,28 +2908,28 @@
         <v>10.1</v>
       </c>
       <c r="M20">
-        <v>0.434592</v>
+        <v>0.458736</v>
       </c>
       <c r="N20">
-        <v>9.665407999999999</v>
+        <v>9.641264</v>
       </c>
       <c r="O20">
-        <v>1.4498112</v>
+        <v>1.4461896</v>
       </c>
       <c r="P20">
-        <v>8.2155968</v>
+        <v>8.195074399999999</v>
       </c>
       <c r="Q20">
-        <v>-1.8844032</v>
+        <v>-1.9049256</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1074755539952409</v>
+        <v>0.1081407262497669</v>
       </c>
       <c r="T20">
-        <v>0.8489872157303322</v>
+        <v>0.8581435621880331</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>23.2401884986378</v>
+        <v>22.01702068292002</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2954,22 +2954,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09571743826231117</v>
+        <v>0.09560902224852477</v>
       </c>
       <c r="C21">
-        <v>39.48109042114226</v>
+        <v>39.03314405825132</v>
       </c>
       <c r="D21">
-        <v>48.60109042114226</v>
+        <v>48.63314405825132</v>
       </c>
       <c r="E21">
-        <v>9.120000000000001</v>
+        <v>9.600000000000001</v>
       </c>
       <c r="F21">
-        <v>9.120000000000001</v>
+        <v>9.600000000000001</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2990,28 +2990,28 @@
         <v>10.1</v>
       </c>
       <c r="M21">
-        <v>0.458736</v>
+        <v>0.48288</v>
       </c>
       <c r="N21">
-        <v>9.641264</v>
+        <v>9.61712</v>
       </c>
       <c r="O21">
-        <v>1.4461896</v>
+        <v>1.442568</v>
       </c>
       <c r="P21">
-        <v>8.195074399999999</v>
+        <v>8.174552</v>
       </c>
       <c r="Q21">
-        <v>-1.9049256</v>
+        <v>-1.925447999999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1081407262497669</v>
+        <v>0.108822527810656</v>
       </c>
       <c r="T21">
-        <v>0.8581435621880331</v>
+        <v>0.8675288173071766</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>22.01702068292002</v>
+        <v>20.91616964877402</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3036,22 +3036,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09560902224852477</v>
+        <v>0.0955006062347384</v>
       </c>
       <c r="C22">
-        <v>39.03314405825132</v>
+        <v>38.58524000361763</v>
       </c>
       <c r="D22">
-        <v>48.63314405825132</v>
+        <v>48.66524000361763</v>
       </c>
       <c r="E22">
-        <v>9.600000000000001</v>
+        <v>10.08</v>
       </c>
       <c r="F22">
-        <v>9.600000000000001</v>
+        <v>10.08</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3072,28 +3072,28 @@
         <v>10.1</v>
       </c>
       <c r="M22">
-        <v>0.48288</v>
+        <v>0.507024</v>
       </c>
       <c r="N22">
-        <v>9.61712</v>
+        <v>9.592976</v>
       </c>
       <c r="O22">
-        <v>1.442568</v>
+        <v>1.4389464</v>
       </c>
       <c r="P22">
-        <v>8.174552</v>
+        <v>8.154029599999999</v>
       </c>
       <c r="Q22">
-        <v>-1.925447999999999</v>
+        <v>-1.9459704</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.108822527810656</v>
+        <v>0.1095215901705549</v>
       </c>
       <c r="T22">
-        <v>0.8675288173071766</v>
+        <v>0.8771516738217415</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>20.91616964877402</v>
+        <v>19.92016157026097</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3118,22 +3118,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0955006062347384</v>
+        <v>0.09539219022095202</v>
       </c>
       <c r="C23">
-        <v>38.58524000361763</v>
+        <v>38.13737834106186</v>
       </c>
       <c r="D23">
-        <v>48.66524000361763</v>
+        <v>48.69737834106186</v>
       </c>
       <c r="E23">
-        <v>10.08</v>
+        <v>10.56</v>
       </c>
       <c r="F23">
-        <v>10.08</v>
+        <v>10.56</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3154,28 +3154,28 @@
         <v>10.1</v>
       </c>
       <c r="M23">
-        <v>0.507024</v>
+        <v>0.531168</v>
       </c>
       <c r="N23">
-        <v>9.592976</v>
+        <v>9.568832</v>
       </c>
       <c r="O23">
-        <v>1.4389464</v>
+        <v>1.4353248</v>
       </c>
       <c r="P23">
-        <v>8.154029599999999</v>
+        <v>8.1335072</v>
       </c>
       <c r="Q23">
-        <v>-1.9459704</v>
+        <v>-1.966492799999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1095215901705549</v>
+        <v>0.1102385772063487</v>
       </c>
       <c r="T23">
-        <v>0.8771516738217413</v>
+        <v>0.8870212702469361</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>19.92016157026097</v>
+        <v>19.01469968070366</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3200,22 +3200,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09539219022095202</v>
+        <v>0.09528377420716563</v>
       </c>
       <c r="C24">
-        <v>38.13737834106186</v>
+        <v>37.68955915462619</v>
       </c>
       <c r="D24">
-        <v>48.69737834106186</v>
+        <v>48.72955915462619</v>
       </c>
       <c r="E24">
-        <v>10.56</v>
+        <v>11.04</v>
       </c>
       <c r="F24">
-        <v>10.56</v>
+        <v>11.04</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3236,28 +3236,28 @@
         <v>10.1</v>
       </c>
       <c r="M24">
-        <v>0.531168</v>
+        <v>0.555312</v>
       </c>
       <c r="N24">
-        <v>9.568832</v>
+        <v>9.544687999999999</v>
       </c>
       <c r="O24">
-        <v>1.4353248</v>
+        <v>1.4317032</v>
       </c>
       <c r="P24">
-        <v>8.1335072</v>
+        <v>8.1129848</v>
       </c>
       <c r="Q24">
-        <v>-1.966492799999999</v>
+        <v>-1.9870152</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1102385772063487</v>
+        <v>0.1109741872820333</v>
       </c>
       <c r="T24">
-        <v>0.8870212702469361</v>
+        <v>0.8971472198260318</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>19.01469968070366</v>
+        <v>18.18797360762958</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3282,22 +3282,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09528377420716563</v>
+        <v>0.09517535819337926</v>
       </c>
       <c r="C25">
-        <v>37.68955915462619</v>
+        <v>37.24178252857511</v>
       </c>
       <c r="D25">
-        <v>48.72955915462619</v>
+        <v>48.76178252857511</v>
       </c>
       <c r="E25">
-        <v>11.04</v>
+        <v>11.52</v>
       </c>
       <c r="F25">
-        <v>11.04</v>
+        <v>11.52</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3318,28 +3318,28 @@
         <v>10.1</v>
       </c>
       <c r="M25">
-        <v>0.555312</v>
+        <v>0.5794560000000001</v>
       </c>
       <c r="N25">
-        <v>9.544687999999999</v>
+        <v>9.520543999999999</v>
       </c>
       <c r="O25">
-        <v>1.4317032</v>
+        <v>1.4280816</v>
       </c>
       <c r="P25">
-        <v>8.1129848</v>
+        <v>8.092462399999999</v>
       </c>
       <c r="Q25">
-        <v>-1.9870152</v>
+        <v>-2.007537600000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1109741872820333</v>
+        <v>0.1117291555176043</v>
       </c>
       <c r="T25">
-        <v>0.8971472198260318</v>
+        <v>0.9075396417624724</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3356,7 +3356,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>18.18797360762958</v>
+        <v>17.43014137397835</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3364,22 +3364,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09517535819337926</v>
+        <v>0.09506694217959288</v>
       </c>
       <c r="C26">
-        <v>37.24178252857511</v>
+        <v>36.79404854739616</v>
       </c>
       <c r="D26">
-        <v>48.76178252857511</v>
+        <v>48.79404854739616</v>
       </c>
       <c r="E26">
-        <v>11.52</v>
+        <v>12</v>
       </c>
       <c r="F26">
-        <v>11.52</v>
+        <v>12</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3400,28 +3400,28 @@
         <v>10.1</v>
       </c>
       <c r="M26">
-        <v>0.579456</v>
+        <v>0.6035999999999999</v>
       </c>
       <c r="N26">
-        <v>9.520543999999999</v>
+        <v>9.4964</v>
       </c>
       <c r="O26">
-        <v>1.4280816</v>
+        <v>1.42446</v>
       </c>
       <c r="P26">
-        <v>8.092462399999999</v>
+        <v>8.07194</v>
       </c>
       <c r="Q26">
-        <v>-2.007537600000001</v>
+        <v>-2.02806</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1117291555176043</v>
+        <v>0.1125042562394572</v>
       </c>
       <c r="T26">
-        <v>0.9075396417624724</v>
+        <v>0.9182091949505511</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3438,7 +3438,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>17.43014137397835</v>
+        <v>16.73293571901922</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3446,22 +3446,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09506694217959288</v>
+        <v>0.09495852616580649</v>
       </c>
       <c r="C27">
-        <v>36.79404854739616</v>
+        <v>36.34635729580064</v>
       </c>
       <c r="D27">
-        <v>48.79404854739616</v>
+        <v>48.82635729580065</v>
       </c>
       <c r="E27">
-        <v>12</v>
+        <v>12.48</v>
       </c>
       <c r="F27">
-        <v>12</v>
+        <v>12.48</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3482,28 +3482,28 @@
         <v>10.1</v>
       </c>
       <c r="M27">
-        <v>0.6035999999999999</v>
+        <v>0.627744</v>
       </c>
       <c r="N27">
-        <v>9.4964</v>
+        <v>9.472256</v>
       </c>
       <c r="O27">
-        <v>1.42446</v>
+        <v>1.4208384</v>
       </c>
       <c r="P27">
-        <v>8.07194</v>
+        <v>8.051417600000001</v>
       </c>
       <c r="Q27">
-        <v>-2.02806</v>
+        <v>-2.048582399999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1125042562394572</v>
+        <v>0.1133003056294682</v>
       </c>
       <c r="T27">
-        <v>0.9182091949505511</v>
+        <v>0.9291671144410105</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>16.73293571901922</v>
+        <v>16.08936126828771</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3528,22 +3528,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09495852616580649</v>
+        <v>0.09485011015202012</v>
       </c>
       <c r="C28">
-        <v>36.34635729580064</v>
+        <v>35.89870885872436</v>
       </c>
       <c r="D28">
-        <v>48.82635729580065</v>
+        <v>48.85870885872436</v>
       </c>
       <c r="E28">
-        <v>12.48</v>
+        <v>12.96</v>
       </c>
       <c r="F28">
-        <v>12.48</v>
+        <v>12.96</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3564,28 +3564,28 @@
         <v>10.1</v>
       </c>
       <c r="M28">
-        <v>0.627744</v>
+        <v>0.651888</v>
       </c>
       <c r="N28">
-        <v>9.472256</v>
+        <v>9.448112</v>
       </c>
       <c r="O28">
-        <v>1.4208384</v>
+        <v>1.4172168</v>
       </c>
       <c r="P28">
-        <v>8.051417600000001</v>
+        <v>8.0308952</v>
       </c>
       <c r="Q28">
-        <v>-2.048582399999999</v>
+        <v>-2.0691048</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1133003056294682</v>
+        <v>0.1141181645918084</v>
       </c>
       <c r="T28">
-        <v>0.9291671144410105</v>
+        <v>0.9404252509038113</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>16.08936126828771</v>
+        <v>15.49345899909187</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3610,22 +3610,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09485011015202012</v>
+        <v>0.09474169413823377</v>
       </c>
       <c r="C29">
-        <v>35.89870885872436</v>
+        <v>35.45110332132839</v>
       </c>
       <c r="D29">
-        <v>48.85870885872436</v>
+        <v>48.89110332132839</v>
       </c>
       <c r="E29">
-        <v>12.96</v>
+        <v>13.44</v>
       </c>
       <c r="F29">
-        <v>12.96</v>
+        <v>13.44</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3646,28 +3646,28 @@
         <v>10.1</v>
       </c>
       <c r="M29">
-        <v>0.651888</v>
+        <v>0.6760320000000001</v>
       </c>
       <c r="N29">
-        <v>9.448112</v>
+        <v>9.423968</v>
       </c>
       <c r="O29">
-        <v>1.4172168</v>
+        <v>1.4135952</v>
       </c>
       <c r="P29">
-        <v>8.0308952</v>
+        <v>8.010372800000001</v>
       </c>
       <c r="Q29">
-        <v>-2.0691048</v>
+        <v>-2.089627199999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1141181645918084</v>
+        <v>0.114958741858658</v>
       </c>
       <c r="T29">
-        <v>0.9404252509038113</v>
+        <v>0.9519961133794678</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>15.49345899909187</v>
+        <v>14.94012117769573</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3692,22 +3692,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09474169413823377</v>
+        <v>0.09463327812444738</v>
       </c>
       <c r="C30">
-        <v>35.45110332132839</v>
+        <v>35.00354076899983</v>
       </c>
       <c r="D30">
-        <v>48.89110332132839</v>
+        <v>48.92354076899983</v>
       </c>
       <c r="E30">
-        <v>13.44</v>
+        <v>13.92</v>
       </c>
       <c r="F30">
-        <v>13.44</v>
+        <v>13.92</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3728,28 +3728,28 @@
         <v>10.1</v>
       </c>
       <c r="M30">
-        <v>0.6760320000000001</v>
+        <v>0.700176</v>
       </c>
       <c r="N30">
-        <v>9.423968</v>
+        <v>9.399823999999999</v>
       </c>
       <c r="O30">
-        <v>1.4135952</v>
+        <v>1.4099736</v>
       </c>
       <c r="P30">
-        <v>8.010372800000001</v>
+        <v>7.989850399999999</v>
       </c>
       <c r="Q30">
-        <v>-2.089627199999999</v>
+        <v>-2.110149600000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.114958741858658</v>
+        <v>0.1158229973583766</v>
       </c>
       <c r="T30">
-        <v>0.9519961133794678</v>
+        <v>0.9638929156431706</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3766,7 +3766,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>14.94012117769573</v>
+        <v>14.42494458536139</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3774,22 +3774,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09463327812444737</v>
+        <v>0.094524862110661</v>
       </c>
       <c r="C31">
-        <v>35.00354076899983</v>
+        <v>34.55602128735249</v>
       </c>
       <c r="D31">
-        <v>48.92354076899983</v>
+        <v>48.95602128735248</v>
       </c>
       <c r="E31">
-        <v>13.92</v>
+        <v>14.4</v>
       </c>
       <c r="F31">
-        <v>13.92</v>
+        <v>14.4</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3810,28 +3810,28 @@
         <v>10.1</v>
       </c>
       <c r="M31">
-        <v>0.7001759999999999</v>
+        <v>0.7243199999999999</v>
       </c>
       <c r="N31">
-        <v>9.399823999999999</v>
+        <v>9.375679999999999</v>
       </c>
       <c r="O31">
-        <v>1.4099736</v>
+        <v>1.406352</v>
       </c>
       <c r="P31">
-        <v>7.989850399999999</v>
+        <v>7.969327999999999</v>
       </c>
       <c r="Q31">
-        <v>-2.110149600000001</v>
+        <v>-2.130672000000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1158229973583766</v>
+        <v>0.1167119458723729</v>
       </c>
       <c r="T31">
-        <v>0.9638929156431706</v>
+        <v>0.9761296265429793</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>14.42494458536139</v>
+        <v>13.94411309918268</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3856,22 +3856,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.094524862110661</v>
+        <v>0.09441644609687462</v>
       </c>
       <c r="C32">
-        <v>34.55602128735249</v>
+        <v>34.1085449622277</v>
       </c>
       <c r="D32">
-        <v>48.95602128735248</v>
+        <v>48.9885449622277</v>
       </c>
       <c r="E32">
-        <v>14.4</v>
+        <v>14.88</v>
       </c>
       <c r="F32">
-        <v>14.4</v>
+        <v>14.88</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3892,28 +3892,28 @@
         <v>10.1</v>
       </c>
       <c r="M32">
-        <v>0.7243199999999999</v>
+        <v>0.7484639999999999</v>
       </c>
       <c r="N32">
-        <v>9.375679999999999</v>
+        <v>9.351535999999999</v>
       </c>
       <c r="O32">
-        <v>1.406352</v>
+        <v>1.4027304</v>
       </c>
       <c r="P32">
-        <v>7.969327999999999</v>
+        <v>7.9488056</v>
       </c>
       <c r="Q32">
-        <v>-2.130672000000001</v>
+        <v>-2.1511944</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1167119458723729</v>
+        <v>0.1176266610099632</v>
       </c>
       <c r="T32">
-        <v>0.9761296265429793</v>
+        <v>0.9887210247152464</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>13.94411309918268</v>
+        <v>13.49430299920905</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3938,22 +3938,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09441644609687462</v>
+        <v>0.09430803008308823</v>
       </c>
       <c r="C33">
-        <v>34.1085449622277</v>
+        <v>33.66111187969508</v>
       </c>
       <c r="D33">
-        <v>48.9885449622277</v>
+        <v>49.02111187969508</v>
       </c>
       <c r="E33">
-        <v>14.88</v>
+        <v>15.36</v>
       </c>
       <c r="F33">
-        <v>14.88</v>
+        <v>15.36</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3974,28 +3974,28 @@
         <v>10.1</v>
       </c>
       <c r="M33">
-        <v>0.7484639999999999</v>
+        <v>0.772608</v>
       </c>
       <c r="N33">
-        <v>9.351535999999999</v>
+        <v>9.327392</v>
       </c>
       <c r="O33">
-        <v>1.4027304</v>
+        <v>1.3991088</v>
       </c>
       <c r="P33">
-        <v>7.9488056</v>
+        <v>7.9282832</v>
       </c>
       <c r="Q33">
-        <v>-2.1511944</v>
+        <v>-2.1717168</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1176266610099632</v>
+        <v>0.1185682795339533</v>
       </c>
       <c r="T33">
-        <v>0.9887210247152464</v>
+        <v>1.001682758127874</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4012,7 +4012,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>13.49430299920905</v>
+        <v>13.07260603048376</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4020,22 +4020,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09430803008308823</v>
+        <v>0.09462036406930185</v>
       </c>
       <c r="C34">
-        <v>33.66111187969508</v>
+        <v>33.08740744908837</v>
       </c>
       <c r="D34">
-        <v>49.02111187969508</v>
+        <v>48.92740744908837</v>
       </c>
       <c r="E34">
-        <v>15.36</v>
+        <v>15.84</v>
       </c>
       <c r="F34">
-        <v>15.36</v>
+        <v>15.84</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4056,45 +4056,45 @@
         <v>10.1</v>
       </c>
       <c r="M34">
-        <v>0.772608</v>
+        <v>0.820512</v>
       </c>
       <c r="N34">
-        <v>9.327392</v>
+        <v>9.279487999999999</v>
       </c>
       <c r="O34">
-        <v>1.3991088</v>
+        <v>1.3919232</v>
       </c>
       <c r="P34">
-        <v>7.9282832</v>
+        <v>7.887564799999999</v>
       </c>
       <c r="Q34">
-        <v>-2.1717168</v>
+        <v>-2.212435200000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1185682795339533</v>
+        <v>0.1195380060735849</v>
       </c>
       <c r="T34">
-        <v>1.001682758127874</v>
+        <v>1.015031408955804</v>
       </c>
       <c r="U34">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V34">
         <v>0.15</v>
       </c>
       <c r="W34">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y34">
-        <v>13.07260603048376</v>
+        <v>12.30938730938731</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4102,22 +4102,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09462036406930185</v>
+        <v>0.09452469805551547</v>
       </c>
       <c r="C35">
-        <v>33.08740744908837</v>
+        <v>32.63607046956285</v>
       </c>
       <c r="D35">
-        <v>48.92740744908837</v>
+        <v>48.95607046956285</v>
       </c>
       <c r="E35">
-        <v>15.84</v>
+        <v>16.32</v>
       </c>
       <c r="F35">
-        <v>15.84</v>
+        <v>16.32</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4138,28 +4138,28 @@
         <v>10.1</v>
       </c>
       <c r="M35">
-        <v>0.820512</v>
+        <v>0.845376</v>
       </c>
       <c r="N35">
-        <v>9.279487999999999</v>
+        <v>9.254624</v>
       </c>
       <c r="O35">
-        <v>1.3919232</v>
+        <v>1.3881936</v>
       </c>
       <c r="P35">
-        <v>7.887564799999999</v>
+        <v>7.8664304</v>
       </c>
       <c r="Q35">
-        <v>-2.212435200000001</v>
+        <v>-2.2335696</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1195380060735849</v>
+        <v>0.1205371182659326</v>
       </c>
       <c r="T35">
-        <v>1.015031408955804</v>
+        <v>1.028784564354278</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>12.30938730938731</v>
+        <v>11.94734650617004</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4184,22 +4184,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09452469805551547</v>
+        <v>0.09442903204172909</v>
       </c>
       <c r="C36">
-        <v>32.63607046956285</v>
+        <v>32.18476709289368</v>
       </c>
       <c r="D36">
-        <v>48.95607046956285</v>
+        <v>48.98476709289368</v>
       </c>
       <c r="E36">
-        <v>16.32</v>
+        <v>16.8</v>
       </c>
       <c r="F36">
-        <v>16.32</v>
+        <v>16.8</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4220,28 +4220,28 @@
         <v>10.1</v>
       </c>
       <c r="M36">
-        <v>0.845376</v>
+        <v>0.87024</v>
       </c>
       <c r="N36">
-        <v>9.254624</v>
+        <v>9.229759999999999</v>
       </c>
       <c r="O36">
-        <v>1.3881936</v>
+        <v>1.384464</v>
       </c>
       <c r="P36">
-        <v>7.8664304</v>
+        <v>7.845295999999999</v>
       </c>
       <c r="Q36">
-        <v>-2.2335696</v>
+        <v>-2.254704</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1205371182659326</v>
+        <v>0.1215669723718909</v>
       </c>
       <c r="T36">
-        <v>1.028784564354278</v>
+        <v>1.042960893765012</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.94734650617004</v>
+        <v>11.60599374885089</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4266,22 +4266,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09442903204172909</v>
+        <v>0.09433336602794271</v>
       </c>
       <c r="C37">
-        <v>32.18476709289368</v>
+        <v>31.73349737820659</v>
       </c>
       <c r="D37">
-        <v>48.98476709289368</v>
+        <v>49.01349737820659</v>
       </c>
       <c r="E37">
-        <v>16.8</v>
+        <v>17.28</v>
       </c>
       <c r="F37">
-        <v>16.8</v>
+        <v>17.28</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4302,28 +4302,28 @@
         <v>10.1</v>
       </c>
       <c r="M37">
-        <v>0.87024</v>
+        <v>0.895104</v>
       </c>
       <c r="N37">
-        <v>9.229759999999999</v>
+        <v>9.204896</v>
       </c>
       <c r="O37">
-        <v>1.384464</v>
+        <v>1.3807344</v>
       </c>
       <c r="P37">
-        <v>7.845295999999999</v>
+        <v>7.8241616</v>
       </c>
       <c r="Q37">
-        <v>-2.254704</v>
+        <v>-2.2758384</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1215669723718909</v>
+        <v>0.1226290094186605</v>
       </c>
       <c r="T37">
-        <v>1.042960893765012</v>
+        <v>1.057580233469831</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.60599374885089</v>
+        <v>11.28360503360503</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4348,22 +4348,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09433336602794272</v>
+        <v>0.09423770001415634</v>
       </c>
       <c r="C38">
-        <v>31.73349737820659</v>
+        <v>31.28226138476607</v>
       </c>
       <c r="D38">
-        <v>49.01349737820659</v>
+        <v>49.04226138476607</v>
       </c>
       <c r="E38">
-        <v>17.28</v>
+        <v>17.76</v>
       </c>
       <c r="F38">
-        <v>17.28</v>
+        <v>17.76</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4384,28 +4384,28 @@
         <v>10.1</v>
       </c>
       <c r="M38">
-        <v>0.895104</v>
+        <v>0.9199679999999999</v>
       </c>
       <c r="N38">
-        <v>9.204896</v>
+        <v>9.180032000000001</v>
       </c>
       <c r="O38">
-        <v>1.3807344</v>
+        <v>1.3770048</v>
       </c>
       <c r="P38">
-        <v>7.8241616</v>
+        <v>7.803027200000001</v>
       </c>
       <c r="Q38">
-        <v>-2.2758384</v>
+        <v>-2.296972799999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1226290094186605</v>
+        <v>0.1237247619272323</v>
       </c>
       <c r="T38">
-        <v>1.057580233469831</v>
+        <v>1.072663679197026</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4422,7 +4422,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>11.28360503360503</v>
+        <v>10.97864273539949</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4430,22 +4430,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09423770001415634</v>
+        <v>0.09414203400036997</v>
       </c>
       <c r="C39">
-        <v>31.28226138476607</v>
+        <v>30.83105917197582</v>
       </c>
       <c r="D39">
-        <v>49.04226138476607</v>
+        <v>49.07105917197582</v>
       </c>
       <c r="E39">
-        <v>17.76</v>
+        <v>18.24</v>
       </c>
       <c r="F39">
-        <v>17.76</v>
+        <v>18.24</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4466,28 +4466,28 @@
         <v>10.1</v>
       </c>
       <c r="M39">
-        <v>0.9199679999999999</v>
+        <v>0.9448320000000001</v>
       </c>
       <c r="N39">
-        <v>9.180032000000001</v>
+        <v>9.155168</v>
       </c>
       <c r="O39">
-        <v>1.3770048</v>
+        <v>1.3732752</v>
       </c>
       <c r="P39">
-        <v>7.803027200000001</v>
+        <v>7.7818928</v>
       </c>
       <c r="Q39">
-        <v>-2.296972799999999</v>
+        <v>-2.3181072</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1237247619272323</v>
+        <v>0.1248558612909193</v>
       </c>
       <c r="T39">
-        <v>1.072663679197026</v>
+        <v>1.088233687689614</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4504,7 +4504,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.97864273539949</v>
+        <v>10.68973108446792</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4512,22 +4512,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09414203400036997</v>
+        <v>0.09404636798658358</v>
       </c>
       <c r="C40">
-        <v>30.83105917197582</v>
+        <v>30.37989079937915</v>
       </c>
       <c r="D40">
-        <v>49.07105917197582</v>
+        <v>49.09989079937915</v>
       </c>
       <c r="E40">
-        <v>18.24</v>
+        <v>18.72</v>
       </c>
       <c r="F40">
-        <v>18.24</v>
+        <v>18.72</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4548,28 +4548,28 @@
         <v>10.1</v>
       </c>
       <c r="M40">
-        <v>0.9448320000000001</v>
+        <v>0.9696959999999999</v>
       </c>
       <c r="N40">
-        <v>9.155168</v>
+        <v>9.130303999999999</v>
       </c>
       <c r="O40">
-        <v>1.3732752</v>
+        <v>1.3695456</v>
       </c>
       <c r="P40">
-        <v>7.7818928</v>
+        <v>7.760758399999999</v>
       </c>
       <c r="Q40">
-        <v>-2.3181072</v>
+        <v>-2.3392416</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1248558612909193</v>
+        <v>0.1260240458796452</v>
       </c>
       <c r="T40">
-        <v>1.088233687689614</v>
+        <v>1.104314188263927</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4586,7 +4586,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.68973108446792</v>
+        <v>10.41563541563542</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4594,22 +4594,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09404636798658358</v>
+        <v>0.09395070197279722</v>
       </c>
       <c r="C41">
-        <v>30.37989079937915</v>
+        <v>29.9287563266594</v>
       </c>
       <c r="D41">
-        <v>49.09989079937915</v>
+        <v>49.12875632665941</v>
       </c>
       <c r="E41">
-        <v>18.72</v>
+        <v>19.2</v>
       </c>
       <c r="F41">
-        <v>18.72</v>
+        <v>19.2</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4630,28 +4630,28 @@
         <v>10.1</v>
       </c>
       <c r="M41">
-        <v>0.9696959999999999</v>
+        <v>0.9945600000000001</v>
       </c>
       <c r="N41">
-        <v>9.130303999999999</v>
+        <v>9.10544</v>
       </c>
       <c r="O41">
-        <v>1.3695456</v>
+        <v>1.365816</v>
       </c>
       <c r="P41">
-        <v>7.760758399999999</v>
+        <v>7.739624</v>
       </c>
       <c r="Q41">
-        <v>-2.3392416</v>
+        <v>-2.360376</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1260240458796452</v>
+        <v>0.127231169954662</v>
       </c>
       <c r="T41">
-        <v>1.104314188263927</v>
+        <v>1.12093070552405</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>10.41563541563542</v>
+        <v>10.15524453024453</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4676,22 +4676,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09395070197279722</v>
+        <v>0.09385503595901082</v>
       </c>
       <c r="C42">
-        <v>29.9287563266594</v>
+        <v>29.47765581364035</v>
       </c>
       <c r="D42">
-        <v>49.12875632665941</v>
+        <v>49.15765581364035</v>
       </c>
       <c r="E42">
-        <v>19.2</v>
+        <v>19.68</v>
       </c>
       <c r="F42">
-        <v>19.2</v>
+        <v>19.68</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4712,28 +4712,28 @@
         <v>10.1</v>
       </c>
       <c r="M42">
-        <v>0.9945600000000001</v>
+        <v>1.019424</v>
       </c>
       <c r="N42">
-        <v>9.10544</v>
+        <v>9.080576000000001</v>
       </c>
       <c r="O42">
-        <v>1.365816</v>
+        <v>1.3620864</v>
       </c>
       <c r="P42">
-        <v>7.739624</v>
+        <v>7.718489600000001</v>
       </c>
       <c r="Q42">
-        <v>-2.360376</v>
+        <v>-2.381510399999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.127231169954662</v>
+        <v>0.1284792134898489</v>
       </c>
       <c r="T42">
-        <v>1.12093070552405</v>
+        <v>1.138110494555702</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>10.15524453024453</v>
+        <v>9.907555639262958</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4758,22 +4758,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09385503595901082</v>
+        <v>0.09436626994522446</v>
       </c>
       <c r="C43">
-        <v>29.47765581364035</v>
+        <v>28.84361191759942</v>
       </c>
       <c r="D43">
-        <v>49.15765581364035</v>
+        <v>49.00361191759943</v>
       </c>
       <c r="E43">
-        <v>19.68</v>
+        <v>20.16</v>
       </c>
       <c r="F43">
-        <v>19.68</v>
+        <v>20.16</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4794,45 +4794,45 @@
         <v>10.1</v>
       </c>
       <c r="M43">
-        <v>1.019424</v>
+        <v>1.07856</v>
       </c>
       <c r="N43">
-        <v>9.080576000000001</v>
+        <v>9.02144</v>
       </c>
       <c r="O43">
-        <v>1.3620864</v>
+        <v>1.353216</v>
       </c>
       <c r="P43">
-        <v>7.718489600000001</v>
+        <v>7.668224</v>
       </c>
       <c r="Q43">
-        <v>-2.381510399999999</v>
+        <v>-2.431775999999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1284792134898489</v>
+        <v>0.1297702930090077</v>
       </c>
       <c r="T43">
-        <v>1.138110494555702</v>
+        <v>1.155882690105687</v>
       </c>
       <c r="U43">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V43">
         <v>0.15</v>
       </c>
       <c r="W43">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>9.907555639262958</v>
+        <v>9.364337635365672</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4840,22 +4840,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09436626994522446</v>
+        <v>0.09428505393143807</v>
       </c>
       <c r="C44">
-        <v>28.84361191759943</v>
+        <v>28.38801921143717</v>
       </c>
       <c r="D44">
-        <v>49.00361191759943</v>
+        <v>49.02801921143717</v>
       </c>
       <c r="E44">
-        <v>20.16</v>
+        <v>20.64</v>
       </c>
       <c r="F44">
-        <v>20.16</v>
+        <v>20.64</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4876,28 +4876,28 @@
         <v>10.1</v>
       </c>
       <c r="M44">
-        <v>1.07856</v>
+        <v>1.10424</v>
       </c>
       <c r="N44">
-        <v>9.02144</v>
+        <v>8.995759999999999</v>
       </c>
       <c r="O44">
-        <v>1.353216</v>
+        <v>1.349364</v>
       </c>
       <c r="P44">
-        <v>7.668224</v>
+        <v>7.646395999999999</v>
       </c>
       <c r="Q44">
-        <v>-2.431775999999999</v>
+        <v>-2.453604</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1297702930090077</v>
+        <v>0.1311066735639264</v>
       </c>
       <c r="T44">
-        <v>1.155882690105687</v>
+        <v>1.174278471464444</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>9.364337635365674</v>
+        <v>9.146562341519958</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4922,22 +4922,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09428505393143807</v>
+        <v>0.09420383791765169</v>
       </c>
       <c r="C45">
-        <v>28.38801921143717</v>
+        <v>27.93245083053691</v>
       </c>
       <c r="D45">
-        <v>49.02801921143717</v>
+        <v>49.05245083053691</v>
       </c>
       <c r="E45">
-        <v>20.64</v>
+        <v>21.12</v>
       </c>
       <c r="F45">
-        <v>20.64</v>
+        <v>21.12</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4958,28 +4958,28 @@
         <v>10.1</v>
       </c>
       <c r="M45">
-        <v>1.10424</v>
+        <v>1.12992</v>
       </c>
       <c r="N45">
-        <v>8.995759999999999</v>
+        <v>8.970079999999999</v>
       </c>
       <c r="O45">
-        <v>1.349364</v>
+        <v>1.345512</v>
       </c>
       <c r="P45">
-        <v>7.646395999999999</v>
+        <v>7.624568</v>
       </c>
       <c r="Q45">
-        <v>-2.453604</v>
+        <v>-2.475432</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1311066735639264</v>
+        <v>0.1324907819958066</v>
       </c>
       <c r="T45">
-        <v>1.174278471464444</v>
+        <v>1.193331245014585</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -4996,7 +4996,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>9.146562341519958</v>
+        <v>8.938685924667233</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5004,22 +5004,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09420383791765169</v>
+        <v>0.09412262190386532</v>
       </c>
       <c r="C46">
-        <v>27.93245083053691</v>
+        <v>27.47690681128204</v>
       </c>
       <c r="D46">
-        <v>49.05245083053691</v>
+        <v>49.07690681128204</v>
       </c>
       <c r="E46">
-        <v>21.12</v>
+        <v>21.6</v>
       </c>
       <c r="F46">
-        <v>21.12</v>
+        <v>21.6</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5040,28 +5040,28 @@
         <v>10.1</v>
       </c>
       <c r="M46">
-        <v>1.12992</v>
+        <v>1.1556</v>
       </c>
       <c r="N46">
-        <v>8.970079999999999</v>
+        <v>8.9444</v>
       </c>
       <c r="O46">
-        <v>1.345512</v>
+        <v>1.34166</v>
       </c>
       <c r="P46">
-        <v>7.624568</v>
+        <v>7.60274</v>
       </c>
       <c r="Q46">
-        <v>-2.475432</v>
+        <v>-2.49726</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1324907819958066</v>
+        <v>0.1339252216433915</v>
       </c>
       <c r="T46">
-        <v>1.193331245014585</v>
+        <v>1.213076846693821</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.938685924667233</v>
+        <v>8.740048459674629</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5086,22 +5086,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09412262190386532</v>
+        <v>0.09404140589007895</v>
       </c>
       <c r="C47">
-        <v>27.47690681128204</v>
+        <v>27.02138719012853</v>
       </c>
       <c r="D47">
-        <v>49.07690681128204</v>
+        <v>49.10138719012853</v>
       </c>
       <c r="E47">
-        <v>21.6</v>
+        <v>22.08</v>
       </c>
       <c r="F47">
-        <v>21.6</v>
+        <v>22.08</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5122,28 +5122,28 @@
         <v>10.1</v>
       </c>
       <c r="M47">
-        <v>1.1556</v>
+        <v>1.18128</v>
       </c>
       <c r="N47">
-        <v>8.9444</v>
+        <v>8.91872</v>
       </c>
       <c r="O47">
-        <v>1.34166</v>
+        <v>1.337808</v>
       </c>
       <c r="P47">
-        <v>7.60274</v>
+        <v>7.580912000000001</v>
       </c>
       <c r="Q47">
-        <v>-2.49726</v>
+        <v>-2.519087999999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1339252216433915</v>
+        <v>0.1354127886853314</v>
       </c>
       <c r="T47">
-        <v>1.213076846693821</v>
+        <v>1.233553766953771</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5160,7 +5160,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.740048459674629</v>
+        <v>8.55004740620344</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5168,22 +5168,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09404140589007895</v>
+        <v>0.09396018987629255</v>
       </c>
       <c r="C48">
-        <v>27.02138719012853</v>
+        <v>26.56589200360519</v>
       </c>
       <c r="D48">
-        <v>49.10138719012853</v>
+        <v>49.12589200360519</v>
       </c>
       <c r="E48">
-        <v>22.08</v>
+        <v>22.56</v>
       </c>
       <c r="F48">
-        <v>22.08</v>
+        <v>22.56</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5204,28 +5204,28 @@
         <v>10.1</v>
       </c>
       <c r="M48">
-        <v>1.18128</v>
+        <v>1.20696</v>
       </c>
       <c r="N48">
-        <v>8.91872</v>
+        <v>8.893039999999999</v>
       </c>
       <c r="O48">
-        <v>1.337808</v>
+        <v>1.333956</v>
       </c>
       <c r="P48">
-        <v>7.580912000000001</v>
+        <v>7.559083999999999</v>
       </c>
       <c r="Q48">
-        <v>-2.519087999999999</v>
+        <v>-2.540916</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1354127886853314</v>
+        <v>0.1369564903326275</v>
       </c>
       <c r="T48">
-        <v>1.233553766953771</v>
+        <v>1.254803401185794</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.55004740620344</v>
+        <v>8.368131503943792</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5250,22 +5250,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09396018987629255</v>
+        <v>0.09387897386250617</v>
       </c>
       <c r="C49">
-        <v>26.56589200360519</v>
+        <v>26.11042128831367</v>
       </c>
       <c r="D49">
-        <v>49.12589200360519</v>
+        <v>49.15042128831367</v>
       </c>
       <c r="E49">
-        <v>22.56</v>
+        <v>23.04</v>
       </c>
       <c r="F49">
-        <v>22.56</v>
+        <v>23.04</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5286,28 +5286,28 @@
         <v>10.1</v>
       </c>
       <c r="M49">
-        <v>1.20696</v>
+        <v>1.23264</v>
       </c>
       <c r="N49">
-        <v>8.893039999999999</v>
+        <v>8.86736</v>
       </c>
       <c r="O49">
-        <v>1.333956</v>
+        <v>1.330104</v>
       </c>
       <c r="P49">
-        <v>7.559083999999999</v>
+        <v>7.537255999999999</v>
       </c>
       <c r="Q49">
-        <v>-2.540916</v>
+        <v>-2.562744</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1369564903326275</v>
+        <v>0.1385595651202042</v>
       </c>
       <c r="T49">
-        <v>1.254803401185794</v>
+        <v>1.276870329042125</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.368131503943792</v>
+        <v>8.193795430944963</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5332,22 +5332,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09387897386250617</v>
+        <v>0.0937977578487198</v>
       </c>
       <c r="C50">
-        <v>26.11042128831367</v>
+        <v>25.65497508092885</v>
       </c>
       <c r="D50">
-        <v>49.15042128831367</v>
+        <v>49.17497508092885</v>
       </c>
       <c r="E50">
-        <v>23.04</v>
+        <v>23.52</v>
       </c>
       <c r="F50">
-        <v>23.04</v>
+        <v>23.52</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5368,28 +5368,28 @@
         <v>10.1</v>
       </c>
       <c r="M50">
-        <v>1.23264</v>
+        <v>1.25832</v>
       </c>
       <c r="N50">
-        <v>8.86736</v>
+        <v>8.84168</v>
       </c>
       <c r="O50">
-        <v>1.330104</v>
+        <v>1.326252</v>
       </c>
       <c r="P50">
-        <v>7.537255999999999</v>
+        <v>7.515428</v>
       </c>
       <c r="Q50">
-        <v>-2.562744</v>
+        <v>-2.584572</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1385595651202042</v>
+        <v>0.1402255055857251</v>
       </c>
       <c r="T50">
-        <v>1.276870329042125</v>
+        <v>1.299802626618313</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>8.193795430944963</v>
+        <v>8.02657511602772</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5414,22 +5414,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0937977578487198</v>
+        <v>0.09371654183493341</v>
       </c>
       <c r="C51">
-        <v>25.65497508092885</v>
+        <v>25.19955341819893</v>
       </c>
       <c r="D51">
-        <v>49.17497508092885</v>
+        <v>49.19955341819893</v>
       </c>
       <c r="E51">
-        <v>23.52</v>
+        <v>24</v>
       </c>
       <c r="F51">
-        <v>23.52</v>
+        <v>24</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5450,28 +5450,28 @@
         <v>10.1</v>
       </c>
       <c r="M51">
-        <v>1.25832</v>
+        <v>1.284</v>
       </c>
       <c r="N51">
-        <v>8.84168</v>
+        <v>8.815999999999999</v>
       </c>
       <c r="O51">
-        <v>1.326252</v>
+        <v>1.3224</v>
       </c>
       <c r="P51">
-        <v>7.515428</v>
+        <v>7.493599999999999</v>
       </c>
       <c r="Q51">
-        <v>-2.584572</v>
+        <v>-2.606400000000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1402255055857251</v>
+        <v>0.1419580836698668</v>
       </c>
       <c r="T51">
-        <v>1.299802626618313</v>
+        <v>1.323652216097548</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5488,7 +5488,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>8.02657511602772</v>
+        <v>7.866043613707165</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5496,22 +5496,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09371654183493341</v>
+        <v>0.09363532582114704</v>
       </c>
       <c r="C52">
-        <v>25.19955341819893</v>
+        <v>24.74415633694557</v>
       </c>
       <c r="D52">
-        <v>49.19955341819893</v>
+        <v>49.22415633694557</v>
       </c>
       <c r="E52">
-        <v>24</v>
+        <v>24.48</v>
       </c>
       <c r="F52">
-        <v>24</v>
+        <v>24.48</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5532,28 +5532,28 @@
         <v>10.1</v>
       </c>
       <c r="M52">
-        <v>1.284</v>
+        <v>1.30968</v>
       </c>
       <c r="N52">
-        <v>8.815999999999999</v>
+        <v>8.790319999999999</v>
       </c>
       <c r="O52">
-        <v>1.3224</v>
+        <v>1.318548</v>
       </c>
       <c r="P52">
-        <v>7.493599999999999</v>
+        <v>7.471772</v>
       </c>
       <c r="Q52">
-        <v>-2.606400000000001</v>
+        <v>-2.628228</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1419580836698668</v>
+        <v>0.1437613792268307</v>
       </c>
       <c r="T52">
-        <v>1.323652216097548</v>
+        <v>1.348475258208589</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5570,7 +5570,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.866043613707165</v>
+        <v>7.711807464418789</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5578,22 +5578,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09363532582114704</v>
+        <v>0.09390770980736066</v>
       </c>
       <c r="C53">
-        <v>24.74415633694557</v>
+        <v>24.18173950839977</v>
       </c>
       <c r="D53">
-        <v>49.22415633694557</v>
+        <v>49.14173950839977</v>
       </c>
       <c r="E53">
-        <v>24.48</v>
+        <v>24.96</v>
       </c>
       <c r="F53">
-        <v>24.48</v>
+        <v>24.96</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5614,45 +5614,45 @@
         <v>10.1</v>
       </c>
       <c r="M53">
-        <v>1.30968</v>
+        <v>1.355328</v>
       </c>
       <c r="N53">
-        <v>8.790319999999999</v>
+        <v>8.744672</v>
       </c>
       <c r="O53">
-        <v>1.318548</v>
+        <v>1.3117008</v>
       </c>
       <c r="P53">
-        <v>7.471772</v>
+        <v>7.4329712</v>
       </c>
       <c r="Q53">
-        <v>-2.628228</v>
+        <v>-2.6670288</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1437613792268307</v>
+        <v>0.1456398120986681</v>
       </c>
       <c r="T53">
-        <v>1.348475258208589</v>
+        <v>1.374332593740923</v>
       </c>
       <c r="U53">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V53">
         <v>0.15</v>
       </c>
       <c r="W53">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y53">
-        <v>7.711807464418789</v>
+        <v>7.452070642678377</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5660,22 +5660,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09390770980736066</v>
+        <v>0.09383329379357429</v>
       </c>
       <c r="C54">
-        <v>24.18173950839977</v>
+        <v>23.72422858779828</v>
       </c>
       <c r="D54">
-        <v>49.14173950839977</v>
+        <v>49.16422858779828</v>
       </c>
       <c r="E54">
-        <v>24.96</v>
+        <v>25.44</v>
       </c>
       <c r="F54">
-        <v>24.96</v>
+        <v>25.44</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5696,28 +5696,28 @@
         <v>10.1</v>
       </c>
       <c r="M54">
-        <v>1.355328</v>
+        <v>1.381392</v>
       </c>
       <c r="N54">
-        <v>8.744672</v>
+        <v>8.718608</v>
       </c>
       <c r="O54">
-        <v>1.3117008</v>
+        <v>1.3077912</v>
       </c>
       <c r="P54">
-        <v>7.4329712</v>
+        <v>7.4108168</v>
       </c>
       <c r="Q54">
-        <v>-2.6670288</v>
+        <v>-2.6891832</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1456398120986681</v>
+        <v>0.1475981782842006</v>
       </c>
       <c r="T54">
-        <v>1.374332593740923</v>
+        <v>1.401290241423568</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5734,7 +5734,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.452070642678377</v>
+        <v>7.311465536212746</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5742,22 +5742,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09383329379357429</v>
+        <v>0.09375887777978792</v>
       </c>
       <c r="C55">
-        <v>23.72422858779828</v>
+        <v>23.26673826029166</v>
       </c>
       <c r="D55">
-        <v>49.16422858779828</v>
+        <v>49.18673826029166</v>
       </c>
       <c r="E55">
-        <v>25.44</v>
+        <v>25.92</v>
       </c>
       <c r="F55">
-        <v>25.44</v>
+        <v>25.92</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5778,28 +5778,28 @@
         <v>10.1</v>
       </c>
       <c r="M55">
-        <v>1.381392</v>
+        <v>1.407456</v>
       </c>
       <c r="N55">
-        <v>8.718608</v>
+        <v>8.692544</v>
       </c>
       <c r="O55">
-        <v>1.3077912</v>
+        <v>1.3038816</v>
       </c>
       <c r="P55">
-        <v>7.4108168</v>
+        <v>7.388662399999999</v>
       </c>
       <c r="Q55">
-        <v>-2.6891832</v>
+        <v>-2.7113376</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1475981782842006</v>
+        <v>0.1496416908256259</v>
       </c>
       <c r="T55">
-        <v>1.401290241423568</v>
+        <v>1.429419960744591</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5816,7 +5816,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.311465536212746</v>
+        <v>7.176068026282882</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5824,22 +5824,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09375887777978792</v>
+        <v>0.09368446176600154</v>
       </c>
       <c r="C56">
-        <v>23.26673826029166</v>
+        <v>22.80926855417832</v>
       </c>
       <c r="D56">
-        <v>49.18673826029166</v>
+        <v>49.20926855417832</v>
       </c>
       <c r="E56">
-        <v>25.92</v>
+        <v>26.4</v>
       </c>
       <c r="F56">
-        <v>25.92</v>
+        <v>26.4</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5860,28 +5860,28 @@
         <v>10.1</v>
       </c>
       <c r="M56">
-        <v>1.407456</v>
+        <v>1.43352</v>
       </c>
       <c r="N56">
-        <v>8.692544</v>
+        <v>8.66648</v>
       </c>
       <c r="O56">
-        <v>1.3038816</v>
+        <v>1.299972</v>
       </c>
       <c r="P56">
-        <v>7.388662399999999</v>
+        <v>7.366508</v>
       </c>
       <c r="Q56">
-        <v>-2.7113376</v>
+        <v>-2.733492</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1496416908256259</v>
+        <v>0.1517760261466701</v>
       </c>
       <c r="T56">
-        <v>1.429419960744591</v>
+        <v>1.458799889813214</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5898,7 +5898,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>7.176068026282882</v>
+        <v>7.045594062168647</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5906,22 +5906,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09368446176600154</v>
+        <v>0.09361004575221515</v>
       </c>
       <c r="C57">
-        <v>22.80926855417832</v>
+        <v>22.3518194978085</v>
       </c>
       <c r="D57">
-        <v>49.20926855417832</v>
+        <v>49.2318194978085</v>
       </c>
       <c r="E57">
-        <v>26.4</v>
+        <v>26.88</v>
       </c>
       <c r="F57">
-        <v>26.4</v>
+        <v>26.88</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5942,28 +5942,28 @@
         <v>10.1</v>
       </c>
       <c r="M57">
-        <v>1.43352</v>
+        <v>1.459584</v>
       </c>
       <c r="N57">
-        <v>8.66648</v>
+        <v>8.640416</v>
       </c>
       <c r="O57">
-        <v>1.299972</v>
+        <v>1.2960624</v>
       </c>
       <c r="P57">
-        <v>7.366508</v>
+        <v>7.3443536</v>
       </c>
       <c r="Q57">
-        <v>-2.733492</v>
+        <v>-2.7556464</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1517760261466701</v>
+        <v>0.1540073767095799</v>
       </c>
       <c r="T57">
-        <v>1.458799889813214</v>
+        <v>1.489515270203138</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5980,7 +5980,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>7.045594062168647</v>
+        <v>6.919779882487064</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5988,22 +5988,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09361004575221515</v>
+        <v>0.09353562973842877</v>
       </c>
       <c r="C58">
-        <v>22.3518194978085</v>
+        <v>21.89439111958447</v>
       </c>
       <c r="D58">
-        <v>49.2318194978085</v>
+        <v>49.25439111958447</v>
       </c>
       <c r="E58">
-        <v>26.88</v>
+        <v>27.36</v>
       </c>
       <c r="F58">
-        <v>26.88</v>
+        <v>27.36</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6024,28 +6024,28 @@
         <v>10.1</v>
       </c>
       <c r="M58">
-        <v>1.459584</v>
+        <v>1.485648</v>
       </c>
       <c r="N58">
-        <v>8.640416</v>
+        <v>8.614352</v>
       </c>
       <c r="O58">
-        <v>1.2960624</v>
+        <v>1.2921528</v>
       </c>
       <c r="P58">
-        <v>7.3443536</v>
+        <v>7.3221992</v>
       </c>
       <c r="Q58">
-        <v>-2.7556464</v>
+        <v>-2.7778008</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1540073767095799</v>
+        <v>0.1563425110196018</v>
       </c>
       <c r="T58">
-        <v>1.489515270203138</v>
+        <v>1.521659272936779</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6062,7 +6062,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.919779882487064</v>
+        <v>6.798380235425888</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6070,22 +6070,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09353562973842877</v>
+        <v>0.09346121372464239</v>
       </c>
       <c r="C59">
-        <v>21.89439111958447</v>
+        <v>21.43698344796059</v>
       </c>
       <c r="D59">
-        <v>49.25439111958447</v>
+        <v>49.27698344796059</v>
       </c>
       <c r="E59">
-        <v>27.36</v>
+        <v>27.84</v>
       </c>
       <c r="F59">
-        <v>27.36</v>
+        <v>27.84</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6106,28 +6106,28 @@
         <v>10.1</v>
       </c>
       <c r="M59">
-        <v>1.485648</v>
+        <v>1.511712</v>
       </c>
       <c r="N59">
-        <v>8.614352</v>
+        <v>8.588287999999999</v>
       </c>
       <c r="O59">
-        <v>1.2921528</v>
+        <v>1.2882432</v>
       </c>
       <c r="P59">
-        <v>7.3221992</v>
+        <v>7.300044799999998</v>
       </c>
       <c r="Q59">
-        <v>-2.7778008</v>
+        <v>-2.799955200000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1563425110196018</v>
+        <v>0.1587888422015295</v>
       </c>
       <c r="T59">
-        <v>1.521659272936779</v>
+        <v>1.555333942467261</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.798380235425888</v>
+        <v>6.681166783090958</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6152,22 +6152,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09346121372464239</v>
+        <v>0.09338679771085602</v>
       </c>
       <c r="C60">
-        <v>21.43698344796059</v>
+        <v>20.97959651144343</v>
       </c>
       <c r="D60">
-        <v>49.27698344796059</v>
+        <v>49.29959651144343</v>
       </c>
       <c r="E60">
-        <v>27.84</v>
+        <v>28.32</v>
       </c>
       <c r="F60">
-        <v>27.84</v>
+        <v>28.32</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6188,28 +6188,28 @@
         <v>10.1</v>
       </c>
       <c r="M60">
-        <v>1.511712</v>
+        <v>1.537776</v>
       </c>
       <c r="N60">
-        <v>8.588288</v>
+        <v>8.562224000000001</v>
       </c>
       <c r="O60">
-        <v>1.2882432</v>
+        <v>1.2843336</v>
       </c>
       <c r="P60">
-        <v>7.3000448</v>
+        <v>7.2778904</v>
       </c>
       <c r="Q60">
-        <v>-2.799955199999999</v>
+        <v>-2.822109599999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1587888422015295</v>
+        <v>0.1613545066118439</v>
       </c>
       <c r="T60">
-        <v>1.55533394246726</v>
+        <v>1.590651278804106</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.68116678309096</v>
+        <v>6.567926668123316</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6234,22 +6234,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09338679771085602</v>
+        <v>0.09331238169706964</v>
       </c>
       <c r="C61">
-        <v>20.97959651144343</v>
+        <v>20.52223033859197</v>
       </c>
       <c r="D61">
-        <v>49.29959651144343</v>
+        <v>49.32223033859196</v>
       </c>
       <c r="E61">
-        <v>28.32</v>
+        <v>28.8</v>
       </c>
       <c r="F61">
-        <v>28.32</v>
+        <v>28.8</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6270,28 +6270,28 @@
         <v>10.1</v>
       </c>
       <c r="M61">
-        <v>1.537776</v>
+        <v>1.56384</v>
       </c>
       <c r="N61">
-        <v>8.562224000000001</v>
+        <v>8.536159999999999</v>
       </c>
       <c r="O61">
-        <v>1.2843336</v>
+        <v>1.280424</v>
       </c>
       <c r="P61">
-        <v>7.2778904</v>
+        <v>7.255735999999999</v>
       </c>
       <c r="Q61">
-        <v>-2.822109599999999</v>
+        <v>-2.844264000000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1613545066118439</v>
+        <v>0.1640484542426741</v>
       </c>
       <c r="T61">
-        <v>1.590651278804106</v>
+        <v>1.627734481957795</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6308,7 +6308,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.567926668123316</v>
+        <v>6.458461223654593</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6316,22 +6316,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09331238169706964</v>
+        <v>0.09323796568328326</v>
       </c>
       <c r="C62">
-        <v>20.52223033859197</v>
+        <v>20.06488495801759</v>
       </c>
       <c r="D62">
-        <v>49.32223033859196</v>
+        <v>49.34488495801759</v>
       </c>
       <c r="E62">
-        <v>28.8</v>
+        <v>29.28</v>
       </c>
       <c r="F62">
-        <v>28.8</v>
+        <v>29.28</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6352,28 +6352,28 @@
         <v>10.1</v>
       </c>
       <c r="M62">
-        <v>1.56384</v>
+        <v>1.589904</v>
       </c>
       <c r="N62">
-        <v>8.536159999999999</v>
+        <v>8.510095999999999</v>
       </c>
       <c r="O62">
-        <v>1.280424</v>
+        <v>1.2765144</v>
       </c>
       <c r="P62">
-        <v>7.255735999999999</v>
+        <v>7.233581599999999</v>
       </c>
       <c r="Q62">
-        <v>-2.844264000000001</v>
+        <v>-2.866418400000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1640484542426741</v>
+        <v>0.1668805530340596</v>
       </c>
       <c r="T62">
-        <v>1.627734481957795</v>
+        <v>1.666719387837314</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6390,7 +6390,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.458461223654593</v>
+        <v>6.352584810152059</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6398,22 +6398,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09323796568328326</v>
+        <v>0.09316354966949689</v>
       </c>
       <c r="C63">
-        <v>20.06488495801759</v>
+        <v>19.60756039838433</v>
       </c>
       <c r="D63">
-        <v>49.34488495801759</v>
+        <v>49.36756039838433</v>
       </c>
       <c r="E63">
-        <v>29.28</v>
+        <v>29.76</v>
       </c>
       <c r="F63">
-        <v>29.28</v>
+        <v>29.76</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6434,28 +6434,28 @@
         <v>10.1</v>
       </c>
       <c r="M63">
-        <v>1.589904</v>
+        <v>1.615968</v>
       </c>
       <c r="N63">
-        <v>8.510095999999999</v>
+        <v>8.484031999999999</v>
       </c>
       <c r="O63">
-        <v>1.2765144</v>
+        <v>1.2726048</v>
       </c>
       <c r="P63">
-        <v>7.233581599999999</v>
+        <v>7.211427199999999</v>
       </c>
       <c r="Q63">
-        <v>-2.866418400000001</v>
+        <v>-2.8885728</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1668805530340596</v>
+        <v>0.1698617096565707</v>
       </c>
       <c r="T63">
-        <v>1.666719387837314</v>
+        <v>1.707756130868387</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.352584810152059</v>
+        <v>6.250123764827026</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6480,22 +6480,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09316354966949689</v>
+        <v>0.0930891336557105</v>
       </c>
       <c r="C64">
-        <v>19.60756039838433</v>
+        <v>19.15025668840889</v>
       </c>
       <c r="D64">
-        <v>49.36756039838433</v>
+        <v>49.39025668840889</v>
       </c>
       <c r="E64">
-        <v>29.76</v>
+        <v>30.24</v>
       </c>
       <c r="F64">
-        <v>29.76</v>
+        <v>30.24</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6516,28 +6516,28 @@
         <v>10.1</v>
       </c>
       <c r="M64">
-        <v>1.615968</v>
+        <v>1.642032</v>
       </c>
       <c r="N64">
-        <v>8.484031999999999</v>
+        <v>8.457967999999999</v>
       </c>
       <c r="O64">
-        <v>1.2726048</v>
+        <v>1.2686952</v>
       </c>
       <c r="P64">
-        <v>7.211427199999999</v>
+        <v>7.189272799999999</v>
       </c>
       <c r="Q64">
-        <v>-2.8885728</v>
+        <v>-2.9107272</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1698617096565707</v>
+        <v>0.1730040098802987</v>
       </c>
       <c r="T64">
-        <v>1.707756130868387</v>
+        <v>1.751011076225463</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>6.250123764827026</v>
+        <v>6.150915451099612</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6562,22 +6562,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0930891336557105</v>
+        <v>0.09355871764192412</v>
       </c>
       <c r="C65">
-        <v>19.15025668840889</v>
+        <v>18.52738595801046</v>
       </c>
       <c r="D65">
-        <v>49.39025668840889</v>
+        <v>49.24738595801045</v>
       </c>
       <c r="E65">
-        <v>30.24</v>
+        <v>30.72</v>
       </c>
       <c r="F65">
-        <v>30.24</v>
+        <v>30.72</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6598,45 +6598,45 @@
         <v>10.1</v>
       </c>
       <c r="M65">
-        <v>1.642032</v>
+        <v>1.698816</v>
       </c>
       <c r="N65">
-        <v>8.457967999999999</v>
+        <v>8.401183999999999</v>
       </c>
       <c r="O65">
-        <v>1.2686952</v>
+        <v>1.2601776</v>
       </c>
       <c r="P65">
-        <v>7.189272799999999</v>
+        <v>7.141006399999999</v>
       </c>
       <c r="Q65">
-        <v>-2.9107272</v>
+        <v>-2.9589936</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1730040098802987</v>
+        <v>0.1763208823386781</v>
       </c>
       <c r="T65">
-        <v>1.751011076225463</v>
+        <v>1.796669074102377</v>
       </c>
       <c r="U65">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V65">
         <v>0.15</v>
       </c>
       <c r="W65">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>6.150915451099612</v>
+        <v>5.945317209162145</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6644,22 +6644,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09355871764192412</v>
+        <v>0.09349280162813775</v>
       </c>
       <c r="C66">
-        <v>18.52738595801046</v>
+        <v>18.06739098786269</v>
       </c>
       <c r="D66">
-        <v>49.24738595801045</v>
+        <v>49.2673909878627</v>
       </c>
       <c r="E66">
-        <v>30.72</v>
+        <v>31.2</v>
       </c>
       <c r="F66">
-        <v>30.72</v>
+        <v>31.2</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6680,28 +6680,28 @@
         <v>10.1</v>
       </c>
       <c r="M66">
-        <v>1.698816</v>
+        <v>1.72536</v>
       </c>
       <c r="N66">
-        <v>8.401183999999999</v>
+        <v>8.374639999999999</v>
       </c>
       <c r="O66">
-        <v>1.2601776</v>
+        <v>1.256196</v>
       </c>
       <c r="P66">
-        <v>7.141006399999999</v>
+        <v>7.118443999999999</v>
       </c>
       <c r="Q66">
-        <v>-2.9589936</v>
+        <v>-2.981556</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1763208823386781</v>
+        <v>0.1798272903661079</v>
       </c>
       <c r="T66">
-        <v>1.796669074102377</v>
+        <v>1.844936100429401</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6718,7 +6718,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.945317209162145</v>
+        <v>5.85385079055965</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6726,22 +6726,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09349280162813775</v>
+        <v>0.09342688561435138</v>
       </c>
       <c r="C67">
-        <v>18.06739098786269</v>
+        <v>17.60741227700851</v>
       </c>
       <c r="D67">
-        <v>49.2673909878627</v>
+        <v>49.28741227700851</v>
       </c>
       <c r="E67">
-        <v>31.2</v>
+        <v>31.68</v>
       </c>
       <c r="F67">
-        <v>31.2</v>
+        <v>31.68</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6762,28 +6762,28 @@
         <v>10.1</v>
       </c>
       <c r="M67">
-        <v>1.72536</v>
+        <v>1.751904</v>
       </c>
       <c r="N67">
-        <v>8.374639999999999</v>
+        <v>8.348096</v>
       </c>
       <c r="O67">
-        <v>1.256196</v>
+        <v>1.2522144</v>
       </c>
       <c r="P67">
-        <v>7.118443999999999</v>
+        <v>7.0958816</v>
       </c>
       <c r="Q67">
-        <v>-2.981556</v>
+        <v>-3.004118399999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1798272903661079</v>
+        <v>0.1835399576892688</v>
       </c>
       <c r="T67">
-        <v>1.844936100429401</v>
+        <v>1.896042363599191</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6800,7 +6800,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.85385079055965</v>
+        <v>5.765156081611777</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6808,22 +6808,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09342688561435138</v>
+        <v>0.093360969600565</v>
       </c>
       <c r="C68">
-        <v>17.60741227700851</v>
+        <v>17.14744984527834</v>
       </c>
       <c r="D68">
-        <v>49.28741227700851</v>
+        <v>49.30744984527834</v>
       </c>
       <c r="E68">
-        <v>31.68</v>
+        <v>32.16</v>
       </c>
       <c r="F68">
-        <v>31.68</v>
+        <v>32.16</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6844,28 +6844,28 @@
         <v>10.1</v>
       </c>
       <c r="M68">
-        <v>1.751904</v>
+        <v>1.778448</v>
       </c>
       <c r="N68">
-        <v>8.348096</v>
+        <v>8.321551999999999</v>
       </c>
       <c r="O68">
-        <v>1.2522144</v>
+        <v>1.2482328</v>
       </c>
       <c r="P68">
-        <v>7.0958816</v>
+        <v>7.073319199999998</v>
       </c>
       <c r="Q68">
-        <v>-3.004118399999999</v>
+        <v>-3.026680800000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1835399576892688</v>
+        <v>0.1874776351532273</v>
       </c>
       <c r="T68">
-        <v>1.896042363599191</v>
+        <v>1.950245976051997</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6882,7 +6882,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.765156081611777</v>
+        <v>5.679108975916078</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6890,22 +6890,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.093360969600565</v>
+        <v>0.09329505358677861</v>
       </c>
       <c r="C69">
-        <v>17.14744984527834</v>
+        <v>16.68750371253484</v>
       </c>
       <c r="D69">
-        <v>49.30744984527834</v>
+        <v>49.32750371253484</v>
       </c>
       <c r="E69">
-        <v>32.16</v>
+        <v>32.64</v>
       </c>
       <c r="F69">
-        <v>32.16</v>
+        <v>32.64</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6926,28 +6926,28 @@
         <v>10.1</v>
       </c>
       <c r="M69">
-        <v>1.778448</v>
+        <v>1.804992</v>
       </c>
       <c r="N69">
-        <v>8.321551999999999</v>
+        <v>8.295007999999999</v>
       </c>
       <c r="O69">
-        <v>1.2482328</v>
+        <v>1.2442512</v>
       </c>
       <c r="P69">
-        <v>7.073319199999998</v>
+        <v>7.050756799999999</v>
       </c>
       <c r="Q69">
-        <v>-3.026680800000001</v>
+        <v>-3.0492432</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1874776351532273</v>
+        <v>0.1916614174586832</v>
       </c>
       <c r="T69">
-        <v>1.950245976051997</v>
+        <v>2.007837314283105</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6964,7 +6964,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.679108975916078</v>
+        <v>5.595592667446724</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6972,22 +6972,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09329505358677861</v>
+        <v>0.09322913757299223</v>
       </c>
       <c r="C70">
-        <v>16.68750371253484</v>
+        <v>16.22757389867303</v>
       </c>
       <c r="D70">
-        <v>49.32750371253484</v>
+        <v>49.34757389867303</v>
       </c>
       <c r="E70">
-        <v>32.64</v>
+        <v>33.12</v>
       </c>
       <c r="F70">
-        <v>32.64</v>
+        <v>33.12</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7008,28 +7008,28 @@
         <v>10.1</v>
       </c>
       <c r="M70">
-        <v>1.804992</v>
+        <v>1.831536</v>
       </c>
       <c r="N70">
-        <v>8.295007999999999</v>
+        <v>8.268464</v>
       </c>
       <c r="O70">
-        <v>1.2442512</v>
+        <v>1.2402696</v>
       </c>
       <c r="P70">
-        <v>7.050756799999999</v>
+        <v>7.0281944</v>
       </c>
       <c r="Q70">
-        <v>-3.0492432</v>
+        <v>-3.071805599999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1916614174586832</v>
+        <v>0.1961151212032008</v>
       </c>
       <c r="T70">
-        <v>2.007837314283105</v>
+        <v>2.069144222722671</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7046,7 +7046,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.595592667446724</v>
+        <v>5.5144971215417</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7054,22 +7054,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09322913757299223</v>
+        <v>0.09316322155920585</v>
       </c>
       <c r="C71">
-        <v>16.22757389867303</v>
+        <v>15.76766042362033</v>
       </c>
       <c r="D71">
-        <v>49.34757389867303</v>
+        <v>49.36766042362034</v>
       </c>
       <c r="E71">
-        <v>33.12</v>
+        <v>33.6</v>
       </c>
       <c r="F71">
-        <v>33.12</v>
+        <v>33.6</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7090,28 +7090,28 @@
         <v>10.1</v>
       </c>
       <c r="M71">
-        <v>1.831536</v>
+        <v>1.85808</v>
       </c>
       <c r="N71">
-        <v>8.268464</v>
+        <v>8.24192</v>
       </c>
       <c r="O71">
-        <v>1.2402696</v>
+        <v>1.236288</v>
       </c>
       <c r="P71">
-        <v>7.0281944</v>
+        <v>7.005632</v>
       </c>
       <c r="Q71">
-        <v>-3.071805599999999</v>
+        <v>-3.094367999999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1961151212032008</v>
+        <v>0.2008657385306862</v>
       </c>
       <c r="T71">
-        <v>2.069144222722671</v>
+        <v>2.134538258391542</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.5144971215417</v>
+        <v>5.435718591233962</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7136,22 +7136,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09316322155920585</v>
+        <v>0.09309730554541948</v>
       </c>
       <c r="C72">
-        <v>15.76766042362033</v>
+        <v>15.30776330733656</v>
       </c>
       <c r="D72">
-        <v>49.36766042362034</v>
+        <v>49.38776330733657</v>
       </c>
       <c r="E72">
-        <v>33.6</v>
+        <v>34.08000000000001</v>
       </c>
       <c r="F72">
-        <v>33.6</v>
+        <v>34.08000000000001</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7172,28 +7172,28 @@
         <v>10.1</v>
       </c>
       <c r="M72">
-        <v>1.85808</v>
+        <v>1.884624</v>
       </c>
       <c r="N72">
-        <v>8.24192</v>
+        <v>8.215375999999999</v>
       </c>
       <c r="O72">
-        <v>1.236288</v>
+        <v>1.2323064</v>
       </c>
       <c r="P72">
-        <v>7.005632</v>
+        <v>6.983069599999999</v>
       </c>
       <c r="Q72">
-        <v>-3.094367999999999</v>
+        <v>-3.1169304</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2008657385306862</v>
+        <v>0.2059439846393776</v>
       </c>
       <c r="T72">
-        <v>2.134538258391542</v>
+        <v>2.204442227554817</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7210,7 +7210,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.435718591233962</v>
+        <v>5.359159174456018</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7218,22 +7218,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09309730554541948</v>
+        <v>0.09303138953163309</v>
       </c>
       <c r="C73">
-        <v>15.30776330733657</v>
+        <v>14.84788256981415</v>
       </c>
       <c r="D73">
-        <v>49.38776330733657</v>
+        <v>49.40788256981415</v>
       </c>
       <c r="E73">
-        <v>34.08</v>
+        <v>34.56</v>
       </c>
       <c r="F73">
-        <v>34.08</v>
+        <v>34.56</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7254,28 +7254,28 @@
         <v>10.1</v>
       </c>
       <c r="M73">
-        <v>1.884624</v>
+        <v>1.911168</v>
       </c>
       <c r="N73">
-        <v>8.215375999999999</v>
+        <v>8.188832</v>
       </c>
       <c r="O73">
-        <v>1.2323064</v>
+        <v>1.2283248</v>
       </c>
       <c r="P73">
-        <v>6.983069599999999</v>
+        <v>6.960507199999999</v>
       </c>
       <c r="Q73">
-        <v>-3.1169304</v>
+        <v>-3.1394928</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2059439846393775</v>
+        <v>0.2113849626129753</v>
       </c>
       <c r="T73">
-        <v>2.204442227554816</v>
+        <v>2.279339337372611</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.359159174456019</v>
+        <v>5.284726408144129</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7300,22 +7300,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09303138953163309</v>
+        <v>0.09296547351784672</v>
       </c>
       <c r="C74">
-        <v>14.84788256981415</v>
+        <v>14.38801823107803</v>
       </c>
       <c r="D74">
-        <v>49.40788256981415</v>
+        <v>49.42801823107803</v>
       </c>
       <c r="E74">
-        <v>34.56</v>
+        <v>35.04</v>
       </c>
       <c r="F74">
-        <v>34.56</v>
+        <v>35.04</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7336,28 +7336,28 @@
         <v>10.1</v>
       </c>
       <c r="M74">
-        <v>1.911168</v>
+        <v>1.937712</v>
       </c>
       <c r="N74">
-        <v>8.188832</v>
+        <v>8.162288</v>
       </c>
       <c r="O74">
-        <v>1.2283248</v>
+        <v>1.2243432</v>
       </c>
       <c r="P74">
-        <v>6.960507199999999</v>
+        <v>6.9379448</v>
       </c>
       <c r="Q74">
-        <v>-3.1394928</v>
+        <v>-3.162055199999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2113849626129753</v>
+        <v>0.2172289759920249</v>
       </c>
       <c r="T74">
-        <v>2.279339337372611</v>
+        <v>2.359784381250984</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7374,7 +7374,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.284726408144129</v>
+        <v>5.212332895703799</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7382,22 +7382,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09296547351784672</v>
+        <v>0.09289955750406034</v>
       </c>
       <c r="C75">
-        <v>14.38801823107803</v>
+        <v>13.92817031118587</v>
       </c>
       <c r="D75">
-        <v>49.42801823107803</v>
+        <v>49.44817031118586</v>
       </c>
       <c r="E75">
-        <v>35.04</v>
+        <v>35.52</v>
       </c>
       <c r="F75">
-        <v>35.04</v>
+        <v>35.52</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7418,28 +7418,28 @@
         <v>10.1</v>
       </c>
       <c r="M75">
-        <v>1.937712</v>
+        <v>1.964256</v>
       </c>
       <c r="N75">
-        <v>8.162288</v>
+        <v>8.135743999999999</v>
       </c>
       <c r="O75">
-        <v>1.2243432</v>
+        <v>1.2203616</v>
       </c>
       <c r="P75">
-        <v>6.9379448</v>
+        <v>6.915382399999999</v>
       </c>
       <c r="Q75">
-        <v>-3.162055199999999</v>
+        <v>-3.1846176</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2172289759920249</v>
+        <v>0.2235225288617705</v>
       </c>
       <c r="T75">
-        <v>2.359784381250984</v>
+        <v>2.446417505427692</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7456,7 +7456,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.212332895703799</v>
+        <v>5.141895964680775</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7464,22 +7464,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09289955750406034</v>
+        <v>0.09283364149027395</v>
       </c>
       <c r="C76">
-        <v>13.92817031118587</v>
+        <v>13.46833883022799</v>
       </c>
       <c r="D76">
-        <v>49.44817031118586</v>
+        <v>49.46833883022799</v>
       </c>
       <c r="E76">
-        <v>35.52</v>
+        <v>36</v>
       </c>
       <c r="F76">
-        <v>35.52</v>
+        <v>36</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7500,28 +7500,28 @@
         <v>10.1</v>
       </c>
       <c r="M76">
-        <v>1.964256</v>
+        <v>1.9908</v>
       </c>
       <c r="N76">
-        <v>8.135743999999999</v>
+        <v>8.1092</v>
       </c>
       <c r="O76">
-        <v>1.2203616</v>
+        <v>1.21638</v>
       </c>
       <c r="P76">
-        <v>6.915382399999999</v>
+        <v>6.89282</v>
       </c>
       <c r="Q76">
-        <v>-3.1846176</v>
+        <v>-3.20718</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2235225288617705</v>
+        <v>0.2303195659610958</v>
       </c>
       <c r="T76">
-        <v>2.446417505427692</v>
+        <v>2.539981279538538</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.141895964680775</v>
+        <v>5.073337351818364</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7546,22 +7546,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09283364149027395</v>
+        <v>0.09276772547648758</v>
       </c>
       <c r="C77">
-        <v>13.46833883022799</v>
+        <v>13.00852380832754</v>
       </c>
       <c r="D77">
-        <v>49.46833883022799</v>
+        <v>49.48852380832754</v>
       </c>
       <c r="E77">
-        <v>36</v>
+        <v>36.48</v>
       </c>
       <c r="F77">
-        <v>36</v>
+        <v>36.48</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7582,28 +7582,28 @@
         <v>10.1</v>
       </c>
       <c r="M77">
-        <v>1.9908</v>
+        <v>2.017344</v>
       </c>
       <c r="N77">
-        <v>8.1092</v>
+        <v>8.082656</v>
       </c>
       <c r="O77">
-        <v>1.21638</v>
+        <v>1.2123984</v>
       </c>
       <c r="P77">
-        <v>6.89282</v>
+        <v>6.8702576</v>
       </c>
       <c r="Q77">
-        <v>-3.20718</v>
+        <v>-3.229742399999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2303195659610958</v>
+        <v>0.2376830228186983</v>
       </c>
       <c r="T77">
-        <v>2.539981279538538</v>
+        <v>2.641342034825287</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7620,7 +7620,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.073337351818364</v>
+        <v>5.006582912978648</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7628,22 +7628,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09276772547648758</v>
+        <v>0.09270180946270121</v>
       </c>
       <c r="C78">
-        <v>13.00852380832754</v>
+        <v>12.54872526564056</v>
       </c>
       <c r="D78">
-        <v>49.48852380832754</v>
+        <v>49.50872526564056</v>
       </c>
       <c r="E78">
-        <v>36.48</v>
+        <v>36.96</v>
       </c>
       <c r="F78">
-        <v>36.48</v>
+        <v>36.96</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7664,28 +7664,28 @@
         <v>10.1</v>
       </c>
       <c r="M78">
-        <v>2.017344</v>
+        <v>2.043888</v>
       </c>
       <c r="N78">
-        <v>8.082656</v>
+        <v>8.056111999999999</v>
       </c>
       <c r="O78">
-        <v>1.2123984</v>
+        <v>1.2084168</v>
       </c>
       <c r="P78">
-        <v>6.8702576</v>
+        <v>6.847695199999999</v>
       </c>
       <c r="Q78">
-        <v>-3.229742399999999</v>
+        <v>-3.252304800000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2376830228186983</v>
+        <v>0.2456867802726139</v>
       </c>
       <c r="T78">
-        <v>2.641342034825287</v>
+        <v>2.751516768832623</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7702,7 +7702,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.006582912978648</v>
+        <v>4.941562355667237</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7710,22 +7710,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09270180946270121</v>
+        <v>0.09263589344891482</v>
       </c>
       <c r="C79">
-        <v>12.54872526564056</v>
+        <v>12.08894322235594</v>
       </c>
       <c r="D79">
-        <v>49.50872526564056</v>
+        <v>49.52894322235593</v>
       </c>
       <c r="E79">
-        <v>36.96</v>
+        <v>37.44</v>
       </c>
       <c r="F79">
-        <v>36.96</v>
+        <v>37.44</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7746,28 +7746,28 @@
         <v>10.1</v>
       </c>
       <c r="M79">
-        <v>2.043888</v>
+        <v>2.070432</v>
       </c>
       <c r="N79">
-        <v>8.056111999999999</v>
+        <v>8.029567999999999</v>
       </c>
       <c r="O79">
-        <v>1.2084168</v>
+        <v>1.2044352</v>
       </c>
       <c r="P79">
-        <v>6.847695199999999</v>
+        <v>6.8251328</v>
       </c>
       <c r="Q79">
-        <v>-3.252304800000001</v>
+        <v>-3.2748672</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2456867802726139</v>
+        <v>0.2544181520405219</v>
       </c>
       <c r="T79">
-        <v>2.751516768832623</v>
+        <v>2.871707387749717</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.941562355667237</v>
+        <v>4.878208992133043</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7792,22 +7792,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09263589344891482</v>
+        <v>0.09256997743512843</v>
       </c>
       <c r="C80">
-        <v>12.08894322235594</v>
+        <v>11.62917769869561</v>
       </c>
       <c r="D80">
-        <v>49.52894322235593</v>
+        <v>49.54917769869562</v>
       </c>
       <c r="E80">
-        <v>37.44</v>
+        <v>37.92</v>
       </c>
       <c r="F80">
-        <v>37.44</v>
+        <v>37.92</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7828,28 +7828,28 @@
         <v>10.1</v>
       </c>
       <c r="M80">
-        <v>2.070432</v>
+        <v>2.096976</v>
       </c>
       <c r="N80">
-        <v>8.029567999999999</v>
+        <v>8.003024</v>
       </c>
       <c r="O80">
-        <v>1.2044352</v>
+        <v>1.2004536</v>
       </c>
       <c r="P80">
-        <v>6.8251328</v>
+        <v>6.8025704</v>
       </c>
       <c r="Q80">
-        <v>-3.2748672</v>
+        <v>-3.297429599999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2544181520405219</v>
+        <v>0.2639810830244212</v>
       </c>
       <c r="T80">
-        <v>2.871707387749717</v>
+        <v>3.003344732277963</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.878208992133043</v>
+        <v>4.816459511219966</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7874,22 +7874,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09256997743512843</v>
+        <v>0.09250406142134206</v>
       </c>
       <c r="C81">
-        <v>11.62917769869561</v>
+        <v>11.16942871491455</v>
       </c>
       <c r="D81">
-        <v>49.54917769869562</v>
+        <v>49.56942871491455</v>
       </c>
       <c r="E81">
-        <v>37.92</v>
+        <v>38.40000000000001</v>
       </c>
       <c r="F81">
-        <v>37.92</v>
+        <v>38.40000000000001</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7910,28 +7910,28 @@
         <v>10.1</v>
       </c>
       <c r="M81">
-        <v>2.096976</v>
+        <v>2.123520000000001</v>
       </c>
       <c r="N81">
-        <v>8.003024</v>
+        <v>7.976479999999999</v>
       </c>
       <c r="O81">
-        <v>1.2004536</v>
+        <v>1.196472</v>
       </c>
       <c r="P81">
-        <v>6.8025704</v>
+        <v>6.780007999999999</v>
       </c>
       <c r="Q81">
-        <v>-3.297429599999999</v>
+        <v>-3.319992000000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2639810830244212</v>
+        <v>0.2745003071067104</v>
       </c>
       <c r="T81">
-        <v>3.003344732277963</v>
+        <v>3.148145811259033</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.816459511219966</v>
+        <v>4.756253767329715</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7956,22 +7956,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09250406142134206</v>
+        <v>0.09243814540755568</v>
       </c>
       <c r="C82">
-        <v>11.16942871491455</v>
+        <v>10.70969629130087</v>
       </c>
       <c r="D82">
-        <v>49.56942871491455</v>
+        <v>49.58969629130087</v>
       </c>
       <c r="E82">
-        <v>38.40000000000001</v>
+        <v>38.88</v>
       </c>
       <c r="F82">
-        <v>38.40000000000001</v>
+        <v>38.88</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -7992,28 +7992,28 @@
         <v>10.1</v>
       </c>
       <c r="M82">
-        <v>2.123520000000001</v>
+        <v>2.150064</v>
       </c>
       <c r="N82">
-        <v>7.976479999999999</v>
+        <v>7.949935999999999</v>
       </c>
       <c r="O82">
-        <v>1.196472</v>
+        <v>1.1924904</v>
       </c>
       <c r="P82">
-        <v>6.780007999999999</v>
+        <v>6.7574456</v>
       </c>
       <c r="Q82">
-        <v>-3.319992000000001</v>
+        <v>-3.3425544</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2745003071067104</v>
+        <v>0.2861268179345037</v>
       </c>
       <c r="T82">
-        <v>3.148145811259033</v>
+        <v>3.308189109080216</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8030,7 +8030,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.756253767329715</v>
+        <v>4.697534585017003</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8038,22 +8038,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09243814540755568</v>
+        <v>0.09237222939376932</v>
       </c>
       <c r="C83">
-        <v>10.70969629130087</v>
+        <v>10.24998044817586</v>
       </c>
       <c r="D83">
-        <v>49.58969629130087</v>
+        <v>49.60998044817586</v>
       </c>
       <c r="E83">
-        <v>38.88</v>
+        <v>39.36</v>
       </c>
       <c r="F83">
-        <v>38.88</v>
+        <v>39.36</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8074,28 +8074,28 @@
         <v>10.1</v>
       </c>
       <c r="M83">
-        <v>2.150064</v>
+        <v>2.176608</v>
       </c>
       <c r="N83">
-        <v>7.949935999999999</v>
+        <v>7.923392</v>
       </c>
       <c r="O83">
-        <v>1.1924904</v>
+        <v>1.1885088</v>
       </c>
       <c r="P83">
-        <v>6.7574456</v>
+        <v>6.7348832</v>
       </c>
       <c r="Q83">
-        <v>-3.3425544</v>
+        <v>-3.3651168</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2861268179345037</v>
+        <v>0.2990451632987185</v>
       </c>
       <c r="T83">
-        <v>3.308189109080216</v>
+        <v>3.486014995548198</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8112,7 +8112,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.697534585017003</v>
+        <v>4.640247577882651</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8120,22 +8120,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09237222939376932</v>
+        <v>0.09230631337998293</v>
       </c>
       <c r="C84">
-        <v>10.24998044817586</v>
+        <v>9.79028120589409</v>
       </c>
       <c r="D84">
-        <v>49.60998044817586</v>
+        <v>49.63028120589409</v>
       </c>
       <c r="E84">
-        <v>39.36</v>
+        <v>39.84</v>
       </c>
       <c r="F84">
-        <v>39.36</v>
+        <v>39.84</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8156,28 +8156,28 @@
         <v>10.1</v>
       </c>
       <c r="M84">
-        <v>2.176608</v>
+        <v>2.203152</v>
       </c>
       <c r="N84">
-        <v>7.923392</v>
+        <v>7.896847999999999</v>
       </c>
       <c r="O84">
-        <v>1.1885088</v>
+        <v>1.1845272</v>
       </c>
       <c r="P84">
-        <v>6.7348832</v>
+        <v>6.7123208</v>
       </c>
       <c r="Q84">
-        <v>-3.3651168</v>
+        <v>-3.3876792</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2990451632987185</v>
+        <v>0.3134833139998997</v>
       </c>
       <c r="T84">
-        <v>3.486014995548198</v>
+        <v>3.684761574541824</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.640247577882651</v>
+        <v>4.584340980558762</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8202,22 +8202,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09230631337998293</v>
+        <v>0.09224039736619656</v>
       </c>
       <c r="C85">
-        <v>9.79028120589409</v>
+        <v>9.330598584843443</v>
       </c>
       <c r="D85">
-        <v>49.63028120589409</v>
+        <v>49.65059858484345</v>
       </c>
       <c r="E85">
-        <v>39.84</v>
+        <v>40.32000000000001</v>
       </c>
       <c r="F85">
-        <v>39.84</v>
+        <v>40.32000000000001</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8238,28 +8238,28 @@
         <v>10.1</v>
       </c>
       <c r="M85">
-        <v>2.203152</v>
+        <v>2.229696000000001</v>
       </c>
       <c r="N85">
-        <v>7.896847999999999</v>
+        <v>7.870303999999999</v>
       </c>
       <c r="O85">
-        <v>1.1845272</v>
+        <v>1.1805456</v>
       </c>
       <c r="P85">
-        <v>6.7123208</v>
+        <v>6.689758399999999</v>
       </c>
       <c r="Q85">
-        <v>-3.3876792</v>
+        <v>-3.410241600000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3134833139998997</v>
+        <v>0.3297262335387287</v>
       </c>
       <c r="T85">
-        <v>3.684761574541824</v>
+        <v>3.908351475909654</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.584340980558762</v>
+        <v>4.529765492694967</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8284,22 +8284,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09224039736619655</v>
+        <v>0.0939807313524102</v>
       </c>
       <c r="C86">
-        <v>9.33059858484345</v>
+        <v>8.319691838536329</v>
       </c>
       <c r="D86">
-        <v>49.65059858484345</v>
+        <v>49.11969183853633</v>
       </c>
       <c r="E86">
-        <v>40.32</v>
+        <v>40.8</v>
       </c>
       <c r="F86">
-        <v>40.32</v>
+        <v>40.8</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8320,45 +8320,45 @@
         <v>10.1</v>
       </c>
       <c r="M86">
-        <v>2.229696</v>
+        <v>2.35824</v>
       </c>
       <c r="N86">
-        <v>7.870303999999999</v>
+        <v>7.741759999999999</v>
       </c>
       <c r="O86">
-        <v>1.1805456</v>
+        <v>1.161264</v>
       </c>
       <c r="P86">
-        <v>6.689758399999999</v>
+        <v>6.580495999999999</v>
       </c>
       <c r="Q86">
-        <v>-3.410241600000001</v>
+        <v>-3.519504</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3297262335387284</v>
+        <v>0.3481348756827345</v>
       </c>
       <c r="T86">
-        <v>3.908351475909651</v>
+        <v>4.161753364126525</v>
       </c>
       <c r="U86">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V86">
         <v>0.15</v>
       </c>
       <c r="W86">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y86">
-        <v>4.529765492694968</v>
+        <v>4.282855010516317</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8366,22 +8366,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.0939807313524102</v>
+        <v>0.09393606533862381</v>
       </c>
       <c r="C87">
-        <v>8.319691838536329</v>
+        <v>7.853175665936952</v>
       </c>
       <c r="D87">
-        <v>49.11969183853633</v>
+        <v>49.13317566593695</v>
       </c>
       <c r="E87">
-        <v>40.8</v>
+        <v>41.28</v>
       </c>
       <c r="F87">
-        <v>40.8</v>
+        <v>41.28</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8402,28 +8402,28 @@
         <v>10.1</v>
       </c>
       <c r="M87">
-        <v>2.35824</v>
+        <v>2.385984</v>
       </c>
       <c r="N87">
-        <v>7.741759999999999</v>
+        <v>7.714015999999999</v>
       </c>
       <c r="O87">
-        <v>1.161264</v>
+        <v>1.1571024</v>
       </c>
       <c r="P87">
-        <v>6.580495999999999</v>
+        <v>6.5569136</v>
       </c>
       <c r="Q87">
-        <v>-3.519504</v>
+        <v>-3.5430864</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3481348756827345</v>
+        <v>0.3691733238473128</v>
       </c>
       <c r="T87">
-        <v>4.161753364126525</v>
+        <v>4.451355522088664</v>
       </c>
       <c r="U87">
         <v>0.0578</v>
@@ -8440,7 +8440,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.282855010516317</v>
+        <v>4.233054370859151</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8448,22 +8448,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09393606533862381</v>
+        <v>0.09389139932483742</v>
       </c>
       <c r="C88">
-        <v>7.853175665936952</v>
+        <v>7.386666898250667</v>
       </c>
       <c r="D88">
-        <v>49.13317566593695</v>
+        <v>49.14666689825066</v>
       </c>
       <c r="E88">
-        <v>41.28</v>
+        <v>41.76</v>
       </c>
       <c r="F88">
-        <v>41.28</v>
+        <v>41.76</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8484,28 +8484,28 @@
         <v>10.1</v>
       </c>
       <c r="M88">
-        <v>2.385984</v>
+        <v>2.413728</v>
       </c>
       <c r="N88">
-        <v>7.714015999999999</v>
+        <v>7.686272</v>
       </c>
       <c r="O88">
-        <v>1.1571024</v>
+        <v>1.1529408</v>
       </c>
       <c r="P88">
-        <v>6.5569136</v>
+        <v>6.5333312</v>
       </c>
       <c r="Q88">
-        <v>-3.5430864</v>
+        <v>-3.5666688</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3691733238473128</v>
+        <v>0.3934484563449032</v>
       </c>
       <c r="T88">
-        <v>4.451355522088664</v>
+        <v>4.785511858198826</v>
       </c>
       <c r="U88">
         <v>0.0578</v>
@@ -8522,7 +8522,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.233054370859151</v>
+        <v>4.184398573492954</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8530,22 +8530,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09389139932483742</v>
+        <v>0.09384673331105103</v>
       </c>
       <c r="C89">
-        <v>7.386666898250667</v>
+        <v>6.920165541578982</v>
       </c>
       <c r="D89">
-        <v>49.14666689825066</v>
+        <v>49.16016554157898</v>
       </c>
       <c r="E89">
-        <v>41.76</v>
+        <v>42.24</v>
       </c>
       <c r="F89">
-        <v>41.76</v>
+        <v>42.24</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8566,28 +8566,28 @@
         <v>10.1</v>
       </c>
       <c r="M89">
-        <v>2.413728</v>
+        <v>2.441472</v>
       </c>
       <c r="N89">
-        <v>7.686272</v>
+        <v>7.658528</v>
       </c>
       <c r="O89">
-        <v>1.1529408</v>
+        <v>1.1487792</v>
       </c>
       <c r="P89">
-        <v>6.5333312</v>
+        <v>6.5097488</v>
       </c>
       <c r="Q89">
-        <v>-3.5666688</v>
+        <v>-3.5902512</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3934484563449032</v>
+        <v>0.4217694442587587</v>
       </c>
       <c r="T89">
-        <v>4.785511858198826</v>
+        <v>5.175360916994016</v>
       </c>
       <c r="U89">
         <v>0.0578</v>
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.184398573492954</v>
+        <v>4.136848589703261</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8612,22 +8612,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09384673331105103</v>
+        <v>0.09380206729726466</v>
       </c>
       <c r="C90">
-        <v>6.920165541578982</v>
+        <v>6.453671602030127</v>
       </c>
       <c r="D90">
-        <v>49.16016554157898</v>
+        <v>49.17367160203013</v>
       </c>
       <c r="E90">
-        <v>42.24</v>
+        <v>42.72</v>
       </c>
       <c r="F90">
-        <v>42.24</v>
+        <v>42.72</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8648,28 +8648,28 @@
         <v>10.1</v>
       </c>
       <c r="M90">
-        <v>2.441472</v>
+        <v>2.469216</v>
       </c>
       <c r="N90">
-        <v>7.658528</v>
+        <v>7.630783999999999</v>
       </c>
       <c r="O90">
-        <v>1.1487792</v>
+        <v>1.1446176</v>
       </c>
       <c r="P90">
-        <v>6.5097488</v>
+        <v>6.486166399999999</v>
       </c>
       <c r="Q90">
-        <v>-3.5902512</v>
+        <v>-3.6138336</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4217694442587587</v>
+        <v>0.455239702702406</v>
       </c>
       <c r="T90">
-        <v>5.175360916994016</v>
+        <v>5.636091622842876</v>
       </c>
       <c r="U90">
         <v>0.0578</v>
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.136848589703261</v>
+        <v>4.090367144875134</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8694,22 +8694,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09380206729726466</v>
+        <v>0.09375740128347829</v>
       </c>
       <c r="C91">
-        <v>6.453671602030127</v>
+        <v>5.987185085718991</v>
       </c>
       <c r="D91">
-        <v>49.17367160203013</v>
+        <v>49.18718508571899</v>
       </c>
       <c r="E91">
-        <v>42.72</v>
+        <v>43.2</v>
       </c>
       <c r="F91">
-        <v>42.72</v>
+        <v>43.2</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8730,28 +8730,28 @@
         <v>10.1</v>
       </c>
       <c r="M91">
-        <v>2.469216</v>
+        <v>2.496960000000001</v>
       </c>
       <c r="N91">
-        <v>7.630783999999999</v>
+        <v>7.603039999999999</v>
       </c>
       <c r="O91">
-        <v>1.1446176</v>
+        <v>1.140456</v>
       </c>
       <c r="P91">
-        <v>6.486166399999999</v>
+        <v>6.462584</v>
       </c>
       <c r="Q91">
-        <v>-3.6138336</v>
+        <v>-3.637416</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.455239702702406</v>
+        <v>0.4954040128347829</v>
       </c>
       <c r="T91">
-        <v>5.636091622842876</v>
+        <v>6.188968469861509</v>
       </c>
       <c r="U91">
         <v>0.0578</v>
@@ -8768,7 +8768,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.090367144875134</v>
+        <v>4.044918621043188</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8776,22 +8776,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09375740128347829</v>
+        <v>0.0937127352696919</v>
       </c>
       <c r="C92">
-        <v>5.987185085718991</v>
+        <v>5.520705998767284</v>
       </c>
       <c r="D92">
-        <v>49.18718508571899</v>
+        <v>49.20070599876728</v>
       </c>
       <c r="E92">
-        <v>43.2</v>
+        <v>43.68</v>
       </c>
       <c r="F92">
-        <v>43.2</v>
+        <v>43.68</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8812,28 +8812,28 @@
         <v>10.1</v>
       </c>
       <c r="M92">
-        <v>2.496960000000001</v>
+        <v>2.524704</v>
       </c>
       <c r="N92">
-        <v>7.603039999999999</v>
+        <v>7.575296</v>
       </c>
       <c r="O92">
-        <v>1.140456</v>
+        <v>1.1362944</v>
       </c>
       <c r="P92">
-        <v>6.462584</v>
+        <v>6.4390016</v>
       </c>
       <c r="Q92">
-        <v>-3.637416</v>
+        <v>-3.6609984</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4954040128347829</v>
+        <v>0.544493725218799</v>
       </c>
       <c r="T92">
-        <v>6.188968469861509</v>
+        <v>6.864706838439837</v>
       </c>
       <c r="U92">
         <v>0.0578</v>
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.044918621043188</v>
+        <v>4.000468965866889</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8858,22 +8858,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.0937127352696919</v>
+        <v>0.09640506925590553</v>
       </c>
       <c r="C93">
-        <v>5.520705998767284</v>
+        <v>4.238769266351156</v>
       </c>
       <c r="D93">
-        <v>49.20070599876728</v>
+        <v>48.39876926635116</v>
       </c>
       <c r="E93">
-        <v>43.68</v>
+        <v>44.16</v>
       </c>
       <c r="F93">
-        <v>43.68</v>
+        <v>44.16</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8894,45 +8894,45 @@
         <v>10.1</v>
       </c>
       <c r="M93">
-        <v>2.524704</v>
+        <v>2.707008</v>
       </c>
       <c r="N93">
-        <v>7.575296</v>
+        <v>7.392992</v>
       </c>
       <c r="O93">
-        <v>1.1362944</v>
+        <v>1.1089488</v>
       </c>
       <c r="P93">
-        <v>6.4390016</v>
+        <v>6.284043199999999</v>
       </c>
       <c r="Q93">
-        <v>-3.6609984</v>
+        <v>-3.8159568</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.544493725218799</v>
+        <v>0.6058558656988193</v>
       </c>
       <c r="T93">
-        <v>6.864706838439837</v>
+        <v>7.70937979916275</v>
       </c>
       <c r="U93">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V93">
         <v>0.15</v>
       </c>
       <c r="W93">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y93">
-        <v>4.000468965866889</v>
+        <v>3.731056576116509</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8940,22 +8940,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09640506925590553</v>
+        <v>0.09639015324211914</v>
       </c>
       <c r="C94">
-        <v>4.238769266351156</v>
+        <v>3.763140118858928</v>
       </c>
       <c r="D94">
-        <v>48.39876926635116</v>
+        <v>48.40314011885893</v>
       </c>
       <c r="E94">
-        <v>44.16</v>
+        <v>44.64</v>
       </c>
       <c r="F94">
-        <v>44.16</v>
+        <v>44.64</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8976,28 +8976,28 @@
         <v>10.1</v>
       </c>
       <c r="M94">
-        <v>2.707008</v>
+        <v>2.736432</v>
       </c>
       <c r="N94">
-        <v>7.392992</v>
+        <v>7.363567999999999</v>
       </c>
       <c r="O94">
-        <v>1.1089488</v>
+        <v>1.1045352</v>
       </c>
       <c r="P94">
-        <v>6.284043199999999</v>
+        <v>6.259032799999999</v>
       </c>
       <c r="Q94">
-        <v>-3.8159568</v>
+        <v>-3.840967200000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6058558656988193</v>
+        <v>0.6847500463159882</v>
       </c>
       <c r="T94">
-        <v>7.70937979916275</v>
+        <v>8.795387891520779</v>
       </c>
       <c r="U94">
         <v>0.0613</v>
@@ -9014,7 +9014,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.731056576116509</v>
+        <v>3.690937688201278</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9022,22 +9022,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09639015324211914</v>
+        <v>0.09637523722833276</v>
       </c>
       <c r="C95">
-        <v>3.763140118858928</v>
+        <v>3.287511760894077</v>
       </c>
       <c r="D95">
-        <v>48.40314011885893</v>
+        <v>48.40751176089408</v>
       </c>
       <c r="E95">
-        <v>44.64</v>
+        <v>45.12</v>
       </c>
       <c r="F95">
-        <v>44.64</v>
+        <v>45.12</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9058,28 +9058,28 @@
         <v>10.1</v>
       </c>
       <c r="M95">
-        <v>2.736432</v>
+        <v>2.765856</v>
       </c>
       <c r="N95">
-        <v>7.363567999999999</v>
+        <v>7.334143999999999</v>
       </c>
       <c r="O95">
-        <v>1.1045352</v>
+        <v>1.1001216</v>
       </c>
       <c r="P95">
-        <v>6.259032799999999</v>
+        <v>6.2340224</v>
       </c>
       <c r="Q95">
-        <v>-3.840967200000001</v>
+        <v>-3.8659776</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6847500463159882</v>
+        <v>0.78994228713888</v>
       </c>
       <c r="T95">
-        <v>8.795387891520779</v>
+        <v>10.24339868133148</v>
       </c>
       <c r="U95">
         <v>0.0613</v>
@@ -9096,7 +9096,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.690937688201278</v>
+        <v>3.651672393645945</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9104,22 +9104,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09637523722833276</v>
+        <v>0.09636032121454638</v>
       </c>
       <c r="C96">
-        <v>3.287511760894077</v>
+        <v>2.81188419267059</v>
       </c>
       <c r="D96">
-        <v>48.40751176089408</v>
+        <v>48.41188419267059</v>
       </c>
       <c r="E96">
-        <v>45.12</v>
+        <v>45.6</v>
       </c>
       <c r="F96">
-        <v>45.12</v>
+        <v>45.6</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9140,28 +9140,28 @@
         <v>10.1</v>
       </c>
       <c r="M96">
-        <v>2.765856</v>
+        <v>2.79528</v>
       </c>
       <c r="N96">
-        <v>7.334143999999999</v>
+        <v>7.30472</v>
       </c>
       <c r="O96">
-        <v>1.1001216</v>
+        <v>1.095708</v>
       </c>
       <c r="P96">
-        <v>6.2340224</v>
+        <v>6.209012</v>
       </c>
       <c r="Q96">
-        <v>-3.8659776</v>
+        <v>-3.890988</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.78994228713888</v>
+        <v>0.937211424290929</v>
       </c>
       <c r="T96">
-        <v>10.24339868133148</v>
+        <v>12.27061378706647</v>
       </c>
       <c r="U96">
         <v>0.0613</v>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.651672393645945</v>
+        <v>3.613233736870725</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9186,22 +9186,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09636032121454638</v>
+        <v>0.09634540520076001</v>
       </c>
       <c r="C97">
-        <v>2.81188419267059</v>
+        <v>2.336257414402432</v>
       </c>
       <c r="D97">
-        <v>48.41188419267059</v>
+        <v>48.41625741440244</v>
       </c>
       <c r="E97">
-        <v>45.6</v>
+        <v>46.08000000000001</v>
       </c>
       <c r="F97">
-        <v>45.6</v>
+        <v>46.08000000000001</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9222,28 +9222,28 @@
         <v>10.1</v>
       </c>
       <c r="M97">
-        <v>2.79528</v>
+        <v>2.824704000000001</v>
       </c>
       <c r="N97">
-        <v>7.30472</v>
+        <v>7.275295999999999</v>
       </c>
       <c r="O97">
-        <v>1.095708</v>
+        <v>1.0912944</v>
       </c>
       <c r="P97">
-        <v>6.209012</v>
+        <v>6.184001599999999</v>
       </c>
       <c r="Q97">
-        <v>-3.890988</v>
+        <v>-3.9159984</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.937211424290929</v>
+        <v>1.158115130019002</v>
       </c>
       <c r="T97">
-        <v>12.27061378706647</v>
+        <v>15.31143644566896</v>
       </c>
       <c r="U97">
         <v>0.0613</v>
@@ -9260,7 +9260,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.613233736870725</v>
+        <v>3.575595885444987</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9268,22 +9268,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09634540520076001</v>
+        <v>0.09633048918697364</v>
       </c>
       <c r="C98">
-        <v>2.336257414402439</v>
+        <v>1.86063142630374</v>
       </c>
       <c r="D98">
-        <v>48.41625741440244</v>
+        <v>48.42063142630374</v>
       </c>
       <c r="E98">
-        <v>46.08</v>
+        <v>46.56</v>
       </c>
       <c r="F98">
-        <v>46.08</v>
+        <v>46.56</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9304,28 +9304,28 @@
         <v>10.1</v>
       </c>
       <c r="M98">
-        <v>2.824704</v>
+        <v>2.854128</v>
       </c>
       <c r="N98">
-        <v>7.275295999999999</v>
+        <v>7.245871999999999</v>
       </c>
       <c r="O98">
-        <v>1.0912944</v>
+        <v>1.0868808</v>
       </c>
       <c r="P98">
-        <v>6.184001599999999</v>
+        <v>6.158991199999999</v>
       </c>
       <c r="Q98">
-        <v>-3.9159984</v>
+        <v>-3.941008800000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.158115130018999</v>
+        <v>1.52628797289912</v>
       </c>
       <c r="T98">
-        <v>15.31143644566892</v>
+        <v>20.37947421000637</v>
       </c>
       <c r="U98">
         <v>0.0613</v>
@@ -9342,7 +9342,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.575595885444988</v>
+        <v>3.538734072192978</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9350,22 +9350,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09633048918697364</v>
+        <v>0.09631557317318724</v>
       </c>
       <c r="C99">
-        <v>1.86063142630374</v>
+        <v>1.385006228588701</v>
       </c>
       <c r="D99">
-        <v>48.42063142630374</v>
+        <v>48.4250062285887</v>
       </c>
       <c r="E99">
-        <v>46.56</v>
+        <v>47.04</v>
       </c>
       <c r="F99">
-        <v>46.56</v>
+        <v>47.04</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9386,28 +9386,28 @@
         <v>10.1</v>
       </c>
       <c r="M99">
-        <v>2.854128</v>
+        <v>2.883552</v>
       </c>
       <c r="N99">
-        <v>7.245871999999999</v>
+        <v>7.216448</v>
       </c>
       <c r="O99">
-        <v>1.0868808</v>
+        <v>1.0824672</v>
       </c>
       <c r="P99">
-        <v>6.158991199999999</v>
+        <v>6.1339808</v>
       </c>
       <c r="Q99">
-        <v>-3.941008800000001</v>
+        <v>-3.9660192</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.52628797289912</v>
+        <v>2.262633658659361</v>
       </c>
       <c r="T99">
-        <v>20.37947421000637</v>
+        <v>30.51554973868128</v>
       </c>
       <c r="U99">
         <v>0.0613</v>
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.538734072192978</v>
+        <v>3.50262454084407</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9432,22 +9432,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09631557317318724</v>
+        <v>0.09865685715940087</v>
       </c>
       <c r="C100">
-        <v>1.385006228588701</v>
+        <v>0.2278588497928098</v>
       </c>
       <c r="D100">
-        <v>48.4250062285887</v>
+        <v>47.74785884979281</v>
       </c>
       <c r="E100">
-        <v>47.04</v>
+        <v>47.52</v>
       </c>
       <c r="F100">
-        <v>47.04</v>
+        <v>47.52</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9468,129 +9468,47 @@
         <v>10.1</v>
       </c>
       <c r="M100">
-        <v>2.883552</v>
+        <v>3.046032</v>
       </c>
       <c r="N100">
-        <v>7.216448</v>
+        <v>7.053967999999999</v>
       </c>
       <c r="O100">
-        <v>1.0824672</v>
+        <v>1.0580952</v>
       </c>
       <c r="P100">
-        <v>6.1339808</v>
+        <v>5.995872799999999</v>
       </c>
       <c r="Q100">
-        <v>-3.9660192</v>
+        <v>-4.104127200000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.262633658659361</v>
+        <v>4.471670715940084</v>
       </c>
       <c r="T100">
-        <v>30.51554973868128</v>
+        <v>60.923776324706</v>
       </c>
       <c r="U100">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V100">
         <v>0.15</v>
       </c>
       <c r="W100">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y100">
-        <v>3.50262454084407</v>
+        <v>3.315789197224455</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09865685715940087</v>
-      </c>
-      <c r="C101">
-        <v>0.2278588497928098</v>
-      </c>
-      <c r="D101">
-        <v>47.74785884979281</v>
-      </c>
-      <c r="E101">
-        <v>47.52</v>
-      </c>
-      <c r="F101">
-        <v>47.52</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>48</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0</v>
-      </c>
-      <c r="K101">
-        <v>-10.1</v>
-      </c>
-      <c r="L101">
-        <v>10.1</v>
-      </c>
-      <c r="M101">
-        <v>3.046032</v>
-      </c>
-      <c r="N101">
-        <v>7.053967999999999</v>
-      </c>
-      <c r="O101">
-        <v>1.0580952</v>
-      </c>
-      <c r="P101">
-        <v>5.995872799999999</v>
-      </c>
-      <c r="Q101">
-        <v>-4.104127200000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.471670715940084</v>
-      </c>
-      <c r="T101">
-        <v>60.923776324706</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.15</v>
-      </c>
-      <c r="W101">
-        <v>0.054485</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.315789197224455</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
